--- a/results/Int Task Remove ACC -0.8/Rando_fi_all.xlsx
+++ b/results/Int Task Remove ACC -0.8/Rando_fi_all.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.0017726161369192694 +/- 0.001432197373332523</t>
+          <t>0.00039731051344741306 +/- 0.0013395236553063068</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -886,157 +886,157 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.0004889975550121828 +/- 0.0008983458714363678</t>
+          <t>0.0006418092909535212 +/- 0.0013698615422380745</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.0006112469437652534 +/- 0.001509668586213768</t>
+          <t>0.003911980440097784 +/- 0.0014321973733324943</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.0030562347188263783 +/- 0.0006410812030380022</t>
+          <t>0.0033007334963325087 +/- 0.0009741673258257538</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.00030562347188261007 +/- 0.0017450002962860899</t>
+          <t>0.00281173594132027 +/- 0.0012361704410853928</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-0.001191931540342328 +/- 0.001292682517271168</t>
+          <t>0.0006112469437652424 +/- 0.0008857809747059534</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.0003667481662592009 +/- 0.000356415152496672</t>
+          <t>0.00024449877750606366 +/- 0.00018337408312956162</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-0.0027506112469438014 +/- 0.0013736066659073187</t>
+          <t>-0.0004584352078239928 +/- 0.0011697835702325706</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.007671149144254241 +/- 0.002973984928458218</t>
+          <t>0.022004889975550068 +/- 0.002199639879638947</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.009535452322738346 +/- 0.002346742520837698</t>
+          <t>0.023288508557457198 +/- 0.003131112096544186</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.0002750611246943424 +/- 0.000890513587061944</t>
+          <t>0.009046454767726152 +/- 0.0012086625876091054</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.0023227383863080207 +/- 0.000948910433756735</t>
+          <t>0.00012224938875301516 +/- 0.0010427091753809307</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.014578239608801901 +/- 0.0022167711254020435</t>
+          <t>0.01167481662591685 +/- 0.0021209476250485986</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.01292787286063567 +/- 0.001634728498816161</t>
+          <t>0.014272616136919292 +/- 0.0019186242195256352</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.010116136919315389 +/- 0.0019351058824299133</t>
+          <t>0.013111246943765253 +/- 0.001524751795020342</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>-0.0016809290953545553 +/- 0.001612869780190562</t>
+          <t>0.003484107579462092 +/- 0.0016298645019527398</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.0018643031784840725 +/- 0.0011793264903162978</t>
+          <t>0.0011002444987774696 +/- 0.0013265607832647136</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.00030562347188261007 +/- 0.0010136383833604413</t>
+          <t>0.00012224938875300407 +/- 0.0012467040375532387</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.00030562347188261007 +/- 0.000985606081699085</t>
+          <t>-0.0016503667481662988 +/- 0.0010427091753809294</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.0003667481662591232 +/- 0.00026643636574209584</t>
+          <t>-1.1102230246251566e-17 +/- 0.0001366789717298073</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.018704156479217582 +/- 0.0012660339350371785</t>
+          <t>0.01849022004889974 +/- 0.0009688794305713533</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.0028728606356967835 +/- 0.0010246365901124927</t>
+          <t>-0.004645476772616152 +/- 0.0010300916593125086</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.0007029339853300454 +/- 0.0007492451511082614</t>
+          <t>-0.0010085574572127442 +/- 0.0007737768277000066</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>-0.00036674816625921204 +/- 0.0011002444987775065</t>
+          <t>0.0002444987775060747 +/- 0.0010657454629683968</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.001039119804401023 +/- 0.0012316284645238304</t>
+          <t>0.0020171149144253995 +/- 0.0013052662899793771</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.00042787286063565854 +/- 0.0006723716381417938</t>
+          <t>-0.00042787286063572516 +/- 0.00039138901206803235</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.0029339853300733186 +/- 0.001957899434969094</t>
+          <t>0.008557457212713903 +/- 0.0022788938731426894</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.002811735941320248 +/- 0.0014451822026328844</t>
+          <t>0.002414425427872835 +/- 0.000970805634124018</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>-0.003270171149144285 +/- 0.001446797112291508</t>
+          <t>-0.007854523227383892 +/- 0.0011520829355116454</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.0031784841075794936 +/- 0.0007128303049932944</t>
+          <t>-0.006968215158924218 +/- 0.0011419035264223316</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0003667481662591343 +/- 0.0003817235940341361</t>
+          <t>-0.002047677261613723 +/- 0.000433296053751766</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.0007029339853300342 +/- 0.0005475694641555214</t>
+          <t>-0.0003667481662591898 +/- 0.00032916655300333327</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1046,122 +1046,122 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.0011613691931540715 +/- 0.0014580513987624234</t>
+          <t>-0.004064792176039156 +/- 0.0012678770484530308</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.0013447432762835887 +/- 0.001473346062737636</t>
+          <t>0.0018948655256723513 +/- 0.000883669455672471</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.0029339853300733186 +/- 0.0005668470963016909</t>
+          <t>9.16870415647586e-05 +/- 0.00019569450603398585</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-0.0003056234718826656 +/- 0.0009066257319187913</t>
+          <t>-0.0013447432762836442 +/- 0.0007128303049933201</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.00021393643031781818 +/- 0.0014723948007880033</t>
+          <t>0.0021393643031784593 +/- 0.0015703218311326776</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.0004278728606356474 +/- 0.0011852517988793052</t>
+          <t>-0.004737163814180945 +/- 0.0009591903928163247</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-0.00021393643031788478 +/- 0.0006418092909535486</t>
+          <t>0.0003667481662591232 +/- 0.0005258145028754676</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.001894865525672329 +/- 0.0008291356947585769</t>
+          <t>-0.00012224938875308178 +/- 0.0010865763346351535</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.002047677261613723 +/- 0.0013184385458510357</t>
+          <t>-0.006265281173594139 +/- 0.0009295175015736673</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>-0.002047677261613723 +/- 0.0012897889881423586</t>
+          <t>-0.004187041564792193 +/- 0.0017182998529181716</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.005867970660146704 +/- 0.001030091659312508</t>
+          <t>-0.0022004889975550503 +/- 0.0011820953304287217</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>-0.001436430317848425 +/- 0.001718299852918165</t>
+          <t>-0.002047677261613712 +/- 0.0025352015045709466</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.0009168704156478858 +/- 0.0008962639546830793</t>
+          <t>0.003025672371638144 +/- 0.0011950620290963987</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.00012224938875302627 +/- 0.00198160942267083</t>
+          <t>-0.0024144254278728903 +/- 0.0007664997679697061</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.0002444987775060747 +/- 0.0005077398449216345</t>
+          <t>0.0004584352078239151 +/- 0.00067306587853134</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>-0.0004584352078239928 +/- 0.0012912365632199029</t>
+          <t>-0.002017114914425455 +/- 0.0008447600831959211</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>-0.0017420537897310906 +/- 0.0011108057362705453</t>
+          <t>0.00012224938875303736 +/- 0.0016972424666155267</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.004003667481662587 +/- 0.0016708969355546154</t>
+          <t>0.0003667481662591232 +/- 0.0006526331449896861</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.0018337408312958047 +/- 0.0011353408081299912</t>
+          <t>-0.003300733496332542 +/- 0.0012807045745572676</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-0.0004889975550122494 +/- 0.0005501222493887736</t>
+          <t>-0.0009168704156479635 +/- 0.000641081203037981</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>-0.0005806845965770635 +/- 0.00034712153702933695</t>
+          <t>0.0003056234718825879 +/- 0.00038658651102301347</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>-3.056234718830097e-05 +/- 0.0002538699224608072</t>
+          <t>-0.00033618581907094434 +/- 0.00016458327650168523</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.0027200488997554673 +/- 0.0011141641890928045</t>
+          <t>0.007793398533007289 +/- 0.0006868033329536594</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.004492665036674792 +/- 0.0019137496582461219</t>
+          <t>0.005470660146699247 +/- 0.0017948712542819026</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1171,147 +1171,147 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0.00033618581907086665 +/- 0.0006758357086643006</t>
+          <t>-0.0021699266503667825 +/- 0.0004822657040971666</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.004278728606356941 +/- 0.0015402937858623737</t>
+          <t>0.00021393643031780707 +/- 0.0011357520890013719</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0.0015586797066014292 +/- 0.0023213304831000295</t>
+          <t>-0.0007946210268948928 +/- 0.0012316284645238298</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>-0.00012224938875308178 +/- 0.0004773991244441758</t>
+          <t>-0.0013141809290953988 +/- 0.0005806845965770214</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-0.001039119804401023 +/- 0.0016469674309666769</t>
+          <t>0.0036674816625916875 +/- 0.000927001888025858</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.004584352078239584 +/- 0.001426970358182018</t>
+          <t>-0.0008557457212714393 +/- 0.0014771449845470159</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>0.003147921760391148 +/- 0.0024717741131535247</t>
+          <t>0.0029951100244498654 +/- 0.0014124963335319463</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>-6.112469437657975e-05 +/- 0.0014959948961516384</t>
+          <t>-0.0005195599022005282 +/- 0.0011274979673408742</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.0004278728606356474 +/- 0.0004145678473792917</t>
+          <t>6.112469437649092e-05 +/- 0.0004054553533441853</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.0015586797066014292 +/- 0.0014101799504962268</t>
+          <t>-0.000794621026894915 +/- 0.0007875365969880841</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>-0.0004889975550122605 +/- 0.0011369850389815399</t>
+          <t>3.056234718823436e-05 +/- 0.0009708056341239939</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>-0.0005501222493887847 +/- 0.0005077398449216386</t>
+          <t>0.0011002444987774473 +/- 0.0003667481662591676</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>-0.0003056234718826767 +/- 0.0017556731804822814</t>
+          <t>0.0008557457212713726 +/- 0.001220964813902091</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>-0.0015586797066014957 +/- 0.0011553214041219893</t>
+          <t>-0.0014975550122249715 +/- 0.0006895179812150524</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>-0.0007946210268948928 +/- 0.001559578340118956</t>
+          <t>0.003025672371638122 +/- 0.0009315251011080782</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>-0.0003667481662591898 +/- 0.00035641515249666434</t>
+          <t>-6.112469437656865e-05 +/- 0.0003817235940341361</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>-0.00024449877750615245 +/- 0.0005077398449216505</t>
+          <t>-0.00024449877750614134 +/- 0.0003291665530033292</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>-0.0004278728606357363 +/- 0.00041456784737929007</t>
+          <t>0.0002750611246943313 +/- 0.0003730609907009091</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>3.056234718825657e-05 +/- 9.168704156476968e-05</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.00064180929095351 +/- 0.0006895179812150637</t>
+          <t>0.0007946210268948373 +/- 0.0007993090972262884</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.0003667481662591232 +/- 0.0014644435881064769</t>
+          <t>0.0018948655256723402 +/- 0.0016672593761596671</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>6.112469437651314e-05 +/- 0.00012224938875302627</t>
+          <t>-0.00015281173594133834 +/- 0.00015281173594133834</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.00021393643031780707 +/- 0.00019569450603398585</t>
+          <t>0.00012224938875302627 +/- 0.0004145678473792999</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.0014975550122248936 +/- 0.000741727451070369</t>
+          <t>0.0013447432762835887 +/- 0.0011120663446613963</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.0018031784841075482 +/- 0.0010269130572378485</t>
+          <t>-0.001711491442542823 +/- 0.0008557457212713957</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>-0.0007334963325183574 +/- 0.0005668470963016909</t>
+          <t>0.0010696821515891908 +/- 0.00041569286395890735</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.0012530562347187856 +/- 0.0008905135870619337</t>
+          <t>-0.0002139364303178959 +/- 0.0008541068834035366</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.0010085574572126776 +/- 0.0010502958604791974</t>
+          <t>-0.0027811735941320583 +/- 0.0011872203300461535</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>-0.0008251833740831604 +/- 0.0007238825967192429</t>
+          <t>-0.00021393643031788478 +/- 0.0008430998914507045</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.005131229725744568 +/- 0.0011810666112946576</t>
+          <t>-0.00056030669419046 +/- 0.0013985143852998459</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1331,157 +1331,157 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.0030964317310527402 +/- 0.001594906196754926</t>
+          <t>0.006222353288115634 +/- 0.0013860218224712533</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.005868475375995219 +/- 0.002528053927472467</t>
+          <t>0.0032733706871129866 +/- 0.0026816290778671247</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.0017398997345915213 +/- 0.0013217891377773254</t>
+          <t>-0.002772043644942446 +/- 0.0015163621506555454</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.005897965202005351 +/- 0.0019020366259625183</t>
+          <t>-0.007637864936596827 +/- 0.0014474068052855204</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.0020642878207019267 +/- 0.002303229040373549</t>
+          <t>0.002359186080802178 +/- 0.002253609339373969</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.00011795930404007171 +/- 0.00019561337601622767</t>
+          <t>0.00011795930404012722 +/- 0.00014447005265606696</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-8.846947803012873e-05 +/- 0.0015269352363314233</t>
+          <t>-0.0014744913005012793 +/- 0.0014566899481248557</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.02931288705396634 +/- 0.0035022194843535403</t>
+          <t>0.025980536714833448 +/- 0.003245087038828505</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.03597758773223233 +/- 0.0028224089918030934</t>
+          <t>0.017988793866116272 +/- 0.003849523768111052</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>-0.007637864936596928 +/- 0.0010587627880280959</t>
+          <t>-0.00604541433205541 +/- 0.0008262415645014479</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-0.0009436744323208957 +/- 0.0014495081955110114</t>
+          <t>-0.006399292244175725 +/- 0.001325730863638407</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.014273075788852795 +/- 0.0015781879280754414</t>
+          <t>0.0018578590386317151 +/- 0.0023850324087992445</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.020937776467118797 +/- 0.0021630340101317716</t>
+          <t>0.011648481273960542 +/- 0.0015051371459952536</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-0.0072250073724565485 +/- 0.00195724488422828</t>
+          <t>-0.01300501327042165 +/- 0.0018811180694564358</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>-0.005337658507814857 +/- 0.0018949364584390869</t>
+          <t>-0.0028900029489825505 +/- 0.0013565319964611996</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.006015924506045378 +/- 0.0014874102285955069</t>
+          <t>0.012887053966381656 +/- 0.0013960248161067129</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.005603066941905 +/- 0.0017195375685182424</t>
+          <t>-0.0009731642583308498 +/- 0.0009236484673173624</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>-0.004747861987614311 +/- 0.0020020529722788016</t>
+          <t>0.0008257151282807906 +/- 0.0011406121855389957</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>-2.948982601006511e-05 +/- 0.000307882822439129</t>
+          <t>0.00017693895606021303 +/- 0.00030073839655518164</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.016012975523444363 +/- 0.0015828648658590093</t>
+          <t>0.010881745797699849 +/- 0.0013670689456206876</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>-0.003450309643173155 +/- 0.0015495493548120826</t>
+          <t>-0.003774697729283338 +/- 0.0014006891285211222</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.0008846947803007654 +/- 0.0009418295147550217</t>
+          <t>0.0026245945148924087 +/- 0.0011755311959890642</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.0043055145974638 +/- 0.0011884070586617465</t>
+          <t>0.0007962253022707588 +/- 0.0015039811265113551</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.0013270421704511537 +/- 0.0015618475584624502</t>
+          <t>0.005249189029784773 +/- 0.0010283453715224226</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2.9489826009987397e-05 +/- 0.0004054180797660593</t>
+          <t>0.00079622530227077 +/- 0.0010554721420332294</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.0027720436449424233 +/- 0.0017154868265702174</t>
+          <t>0.003243880861102977 +/- 0.001126804669686981</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-0.0008552049542908224 +/- 0.0013478495879712823</t>
+          <t>-0.007549395458566754 +/- 0.0016640207584389128</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>-0.00032438808611032763 +/- 0.0013085643015236668</t>
+          <t>0.001533470952521443 +/- 0.0017032768007306084</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.0107342966676497 +/- 0.0019835059535004834</t>
+          <t>-0.009289295193158308 +/- 0.0014993481355218088</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>-0.0004128575641404009 +/- 0.0005469547918310643</t>
+          <t>0.001002654084340937 +/- 0.0008151150080262665</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.0004128575641404009 +/- 0.0004606458080747081</t>
+          <t>0.0012090828664111596 +/- 0.00038336773813033064</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1491,122 +1491,122 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.003804187555293481 +/- 0.0019447640334765606</t>
+          <t>-0.014567974048953037 +/- 0.000988679127941035</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>-0.0008257151282808018 +/- 0.0014673966740931777</t>
+          <t>-0.006222353288115534 +/- 0.001706592308608695</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>-0.0020642878207019046 +/- 0.0008944707100031415</t>
+          <t>-0.0013565319964611744 +/- 0.0005469547918310523</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.0007372456502506508 +/- 0.0006359144397772905</t>
+          <t>0.0016809200825715798 +/- 0.0009961277354205034</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.008286641108817406 +/- 0.0012403267970989592</t>
+          <t>0.003804187555293481 +/- 0.0013922821154954501</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>0.0008846947803007654 +/- 0.001201506858594128</t>
+          <t>-0.0036567384252432335 +/- 0.0014874102285954971</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0.0016219404305514162 +/- 0.001015152726514808</t>
+          <t>-0.0008846947803007543 +/- 0.0008022099975662394</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.0069006192863461545 +/- 0.0012385726924211149</t>
+          <t>0.0046004128575641845 +/- 0.0012385726924211218</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.00822766145679744 +/- 0.0009367372559285444</t>
+          <t>-0.005809495723975178 +/- 0.0011946109761444643</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>-0.0009436744323208957 +/- 0.0014495081955110001</t>
+          <t>0.0029194927749926825 +/- 0.0011531238452383913</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-0.004570923031554164 +/- 0.0013270421704511981</t>
+          <t>-0.010586847537599475 +/- 0.0010750649444740909</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.009554703627248551 +/- 0.0014874102285955073</t>
+          <t>0.002801533470952566 +/- 0.0015784634256647257</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.00563255676791502 +/- 0.0012611857729485682</t>
+          <t>0.0008846947803008321 +/- 0.001331948073209825</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-0.00023591860808026556 +/- 0.0011329621180948806</t>
+          <t>-0.006074904158065409 +/- 0.0012173263014184823</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.0002654084340902196 +/- 0.0005816302837899198</t>
+          <t>-0.0013565319964611744 +/- 0.0008668203159362379</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>0.003715718077263297 +/- 0.0011662471208071577</t>
+          <t>-0.008905927455027962 +/- 0.0009212916161494098</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.0016809200825714688 +/- 0.0018699898392789934</t>
+          <t>0.006871129460336245 +/- 0.0018512941451748032</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-0.014803892657033357 +/- 0.002101033692781676</t>
+          <t>-0.010852255971689696 +/- 0.0015537528601969413</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-0.002624594514892398 +/- 0.0015461783224911064</t>
+          <t>-0.0019168386906516677 +/- 0.0017258478193334734</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-0.0004423473901504327 +/- 0.0005477492073431786</t>
+          <t>-0.0005897965202005029 +/- 0.0005595301079625623</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.00020642878207016713 +/- 0.00047642271959314305</t>
+          <t>-0.0012385726924210693 +/- 0.0008423979272831455</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>-0.00041285756414042305 +/- 0.0007126538468649321</t>
+          <t>-0.0003833677381303247 +/- 0.0006050806407750996</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>-0.00884694780300802 +/- 0.0020303054530296243</t>
+          <t>-0.015393689177233794 +/- 0.0021010336927816957</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.005278678855794683 +/- 0.0014593739937078948</t>
+          <t>0.011707460925980595 +/- 0.0018976880617158447</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1616,147 +1616,147 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-0.0016219404305515273 +/- 0.00035510452901186244</t>
+          <t>-0.00103214391035088 +/- 0.00032970627801530796</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>0.0014744913005012906 +/- 0.0006852816301163351</t>
+          <t>-0.00651725154821583 +/- 0.0009179818588188396</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>0.0009141846063107862 +/- 0.0009551244317724306</t>
+          <t>-0.003981126511353517 +/- 0.0012033149963493407</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>-0.00023591860808024333 +/- 0.0006157656448782366</t>
+          <t>0.000412857564140412 +/- 0.000562630021478608</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>-0.00032438808611032763 +/- 0.0019846017526854846</t>
+          <t>0.0030374520790327876 +/- 0.0009873588347262133</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>-0.011707460925980573 +/- 0.0016154934738781914</t>
+          <t>-0.014951341787083405 +/- 0.001209082866411078</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>8.84694780300177e-05 +/- 0.001134879469471768</t>
+          <t>0.00610439398407554 +/- 0.002147094267091419</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>0.0030669419050427193 +/- 0.0007934900647050197</t>
+          <t>0.008522559716897726 +/- 0.0007034420785536152</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>-8.846947803012873e-05 +/- 0.0002654084340902381</t>
+          <t>0.00017693895606020195 +/- 0.00027027871984407724</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.005101739899734526 +/- 0.0016474759921514023</t>
+          <t>-0.007962253022707099 +/- 0.0015825901344734383</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.007991742848717153 +/- 0.0015573867209095495</t>
+          <t>0.001503981126511411 +/- 0.00120475955268744</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>8.8469478030051e-05 +/- 0.0008851861409497902</t>
+          <t>-0.0016809200825714688 +/- 0.0006731177947810839</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.010763786493659621 +/- 0.0010895283516314527</t>
+          <t>0.025538189324683026 +/- 0.0013526800284493963</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0.00238867590681211 +/- 0.0008070735584431724</t>
+          <t>0.0006487761722206553 +/- 0.0015704543740128992</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0.007048068416396292 +/- 0.001894936458439078</t>
+          <t>0.01574756708935423 +/- 0.0014031704221020575</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>0.00011795930404007171 +/- 0.00019561337601622767</t>
+          <t>0.00023591860808025444 +/- 0.0004530313033246167</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>-0.0013860218224713062 +/- 0.0005445645919380657</t>
+          <t>-0.0005897965202004806 +/- 0.000932550179937595</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.0014450014744912699 +/- 0.0008070735584431692</t>
+          <t>-0.0002948982601002403 +/- 0.0006460897169037833</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
+          <t>-0.0004128575641403565 +/- 0.0002359186080802156</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>0.0005603066941905599 +/- 0.00038336773813036734</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>0.0005897965202005917 +/- 0.0013055702519126381</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0.0020937776467118475 +/- 0.0005509154141040711</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>0.004069595989383612 +/- 0.0010112903685922713</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.0009731642583308386 +/- 0.0005603066941904915</t>
+          <t>-8.8469478030051e-05 +/- 0.00032438808611030145</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.005809495723975178 +/- 0.0012233835749154715</t>
+          <t>0.004777351813624353 +/- 0.0007437051142977651</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.0008257151282806907 +/- 0.0011557604212483327</t>
+          <t>0.0010911235623710213 +/- 0.0011501032143910348</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>-0.000265408434090264 +/- 0.0006248782099798564</t>
+          <t>-0.0008552049542907448 +/- 0.0006909687121120623</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.005131229725744579 +/- 0.0009798435697927735</t>
+          <t>0.004246534945443858 +/- 0.0011587663051836423</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.011736950751990516 +/- 0.0009022151896654876</t>
+          <t>0.002595104688882377 +/- 0.0012840779154867125</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.0007372456502506286 +/- 0.0008470307647505073</t>
+          <t>-0.0012090828664110486 +/- 0.0012817053265762714</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-0.00044391831902932386 +/- 0.0007398638650488598</t>
+          <t>0.0007694584196507703 +/- 0.0012777172622031674</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1776,157 +1776,157 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.005474992601361373 +/- 0.001338315366036698</t>
+          <t>-0.010328499556081727 +/- 0.0017228504975232751</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-0.004971885173128165 +/- 0.0013868451629310173</t>
+          <t>0.001006214856466392 +/- 0.0012429712932820137</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-0.001686889612311382 +/- 0.0008479756603666649</t>
+          <t>0.002426753477360144 +/- 0.0015648776639718622</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-0.005859721811186746 +/- 0.0007463462688912852</t>
+          <t>-0.0035513465522344244 +/- 0.001138525247805347</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.004883101509322319 +/- 0.001762056898088676</t>
+          <t>0.003906481207457802 +/- 0.0012471919210243134</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.9594554601952706e-05 +/- 0.0002458308334690123</t>
+          <t>8.878366380585812e-05 +/- 0.00037551280084194413</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.00479431784551645 +/- 0.0011214735319026975</t>
+          <t>-0.0018052678307191594 +/- 0.001650145233436018</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.005563776265167164 +/- 0.0024540292916990724</t>
+          <t>0.010298905001479708 +/- 0.004159693360358482</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.020479431784551593 +/- 0.0025554345244063826</t>
+          <t>0.012518496596626216 +/- 0.003400284249474387</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.002545131695767933 +/- 0.0005327019828351487</t>
+          <t>0.0017460787215152096 +/- 0.0008922647784362866</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.0009470257472624866 +/- 0.0009054192684686639</t>
+          <t>-0.0007398638650488287 +/- 0.0010933976443865737</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-0.002278780704350447 +/- 0.0017208158342831134</t>
+          <t>-0.0012133767386800832 +/- 0.0009766203018644723</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.004942290618526135 +/- 0.001343540628921727</t>
+          <t>0.0050902633915359315 +/- 0.002253076805051715</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.013879846108316041 +/- 0.001511641644169506</t>
+          <t>0.00905593370819766 +/- 0.0010849542929756485</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-0.0036697247706422463 +/- 0.0015217472781511936</t>
+          <t>-0.007013909440662913 +/- 0.0011692658339827434</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-0.0005622965374371458 +/- 0.0009212419305281982</t>
+          <t>0.001006214856466392 +/- 0.0012499977556639534</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.002545131695767933 +/- 0.0013048480429149573</t>
+          <t>-0.00011837821840782192 +/- 0.000796308022910565</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-0.001272565847884033 +/- 0.0008056026983614516</t>
+          <t>-0.00038472920982540737 +/- 0.0016848115214548975</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>5.918910920390541e-05 +/- 0.00017756732761171621</t>
+          <t>0.00032554010062147977 +/- 0.0004068578598658559</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.001390944066291777 +/- 0.0013693678959762138</t>
+          <t>-0.0008878366380586034 +/- 0.0016370898710789405</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.0031666173424089394 +/- 0.0008883297436995184</t>
+          <t>0.0003551346552234325 +/- 0.0008137157197317118</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.0014797277300976353 +/- 0.001198488116680451</t>
+          <t>-0.0009766203018644615 +/- 0.0011311935397227912</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-0.0027226990233797377 +/- 0.001081720442882354</t>
+          <t>-0.001242971293282047 +/- 0.001281823487878551</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.002989050014797323 +/- 0.00152892469406208</t>
+          <t>-0.0004439183190293128 +/- 0.0016806476311927482</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>-0.00026635099141757433 +/- 0.00030897622103907553</t>
+          <t>0.0 +/- 0.0006065078878934249</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>-0.000532701982835182 +/- 0.0026364081031453124</t>
+          <t>-0.005445398046759409 +/- 0.002764201107744462</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-0.0014797277300977018 +/- 0.0011763602790383063</t>
+          <t>0.0005622965374371014 +/- 0.0009766203018644394</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.0037585084344480047 +/- 0.0011988534537158342</t>
+          <t>0.0032554010062148197 +/- 0.0007717315661678345</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0013317549570878717 +/- 0.001001416058933905</t>
+          <t>0.0040544539804675764 +/- 0.0010256125156060329</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>8.878366380585812e-05 +/- 0.0004960951350766471</t>
+          <t>0.000503107428233196 +/- 0.0005776626604303872</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.00011837821840781082 +/- 0.0007151847276468987</t>
+          <t>0.0004439183190292906 +/- 0.0007034545323471144</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1936,122 +1936,122 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.002012429712932784 +/- 0.0009974725981859965</t>
+          <t>0.0009470257472624866 +/- 0.000617952442078151</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.0008286475288547312 +/- 0.000573859704932427</t>
+          <t>0.00041432376442732675 +/- 0.0013956586117255532</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>-0.0007694584196508037 +/- 0.0003789952197356315</t>
+          <t>-0.0010654039656702973 +/- 0.0006374862157010248</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>-0.0003255401006214909 +/- 0.00046699419467476007</t>
+          <t>0.0005622965374371014 +/- 0.0008312857002182826</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>-0.002574726250369974 +/- 0.0015606743857277548</t>
+          <t>-0.006333234684818001 +/- 0.0018773307519566252</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.0008878366380585812 +/- 0.0009635288899733301</t>
+          <t>0.0014797277300976353 +/- 0.0006748596774780215</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.0005622965374371014 +/- 0.0003361295262385422</t>
+          <t>0.0004735128736312433 +/- 0.0006643961030080865</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-0.0008582420834566728 +/- 0.0013396235925133438</t>
+          <t>-0.002900266350991443 +/- 0.001274972431402079</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.00251553714116598 +/- 0.0013706464843929213</t>
+          <t>0.001509322284699588 +/- 0.0012587256773090474</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.0004143237644273157 +/- 0.001594814274673865</t>
+          <t>-0.00011837821840781082 +/- 0.0010438113103609398</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-0.00029594554601956034 +/- 0.0016370898710789488</t>
+          <t>-2.9594554601974908e-05 +/- 0.0018597534588179886</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>-0.0021308079313406836 +/- 0.0011369856592067836</t>
+          <t>-0.0006806747558449122 +/- 0.00116926583398272</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>-0.0037585084344481045 +/- 0.0011077222416225252</t>
+          <t>-0.0020124297129328283 +/- 0.0010897870754378479</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.003077833678603081 +/- 0.0009188620713974397</t>
+          <t>-0.0005918910920390541 +/- 0.0009073518624892344</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-5.918910920391651e-05 +/- 0.00047351287363126964</t>
+          <t>0.00026635099141757433 +/- 0.0007539354366887698</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.0020420242675347365 +/- 0.0009116852205237694</t>
+          <t>-0.0022491861497484613 +/- 0.0010686871906048087</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.0020716188221366894 +/- 0.0014973791820862134</t>
+          <t>-0.0013909440662917994 +/- 0.0013947169775612046</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.001982835158330831 +/- 0.0012835305381592808</t>
+          <t>-0.0013909440662917994 +/- 0.0015884861675430234</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.008256880733944927 +/- 0.0015961866303831605</t>
+          <t>0.004527966854098842 +/- 0.000837583409179365</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.0020420242675347365 +/- 0.0005985128267581035</t>
+          <t>-0.0010654039656702973 +/- 0.0006510802012429595</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>-0.0010654039656703752 +/- 0.0006510802012429989</t>
+          <t>-0.0018644569399230426 +/- 0.0005302300345418682</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.00014797277300976353 +/- 0.0002728483118464848</t>
+          <t>-0.0004439183190292906 +/- 0.0004025294616376205</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.004527966854098797 +/- 0.0012489463063633957</t>
+          <t>0.0004439183190292906 +/- 0.001163258005743308</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>-0.0026635099141758324 +/- 0.0013561928662195512</t>
+          <t>-0.0019236460491269592 +/- 0.0011404468107722937</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2061,92 +2061,92 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>-0.0004143237644273601 +/- 0.0007273279507218014</t>
+          <t>0.00017756732761171624 +/- 0.0006374862157010247</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.002781888132583554 +/- 0.0008898074210341897</t>
+          <t>-0.0010062148564664141 +/- 0.0012499977556639907</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.0004735128736312322 +/- 0.0014266908308012902</t>
+          <t>-0.0005622965374371236 +/- 0.0015403389972978015</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.0005622965374371014 +/- 0.0006676835852428691</t>
+          <t>-0.0014797277300976463 +/- 0.00045847686844717705</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-0.0005031074282332404 +/- 0.0008479756603666731</t>
+          <t>0.00020716188221366893 +/- 0.0008784150387484795</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-0.00136134951168988 +/- 0.0011999487974379177</t>
+          <t>-0.002841077241787526 +/- 0.0015389168393015883</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-0.00446877774489497 +/- 0.001244731627393472</t>
+          <t>0.0014797277300976463 +/- 0.0016477550644658247</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>-0.0007694584196508147 +/- 0.0009833233338760944</t>
+          <t>-5.918910920390541e-05 +/- 0.0007463462688912852</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>-2.9594554601952706e-05 +/- 0.0002458308334690123</t>
+          <t>-8.878366380585812e-05 +/- 0.0001894976098677932</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.0031370227878069977 +/- 0.001538916839301561</t>
+          <t>0.001686889612311304 +/- 0.0007946565008640017</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.0034625628884284664 +/- 0.0008883297436995184</t>
+          <t>0.002841077241787482 +/- 0.001324831564699587</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>-0.0011837821840781858 +/- 0.0005918910920390986</t>
+          <t>-0.0009470257472624866 +/- 0.000710269310446865</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.005948505474992571 +/- 0.0017926093780299373</t>
+          <t>-0.0005031074282332071 +/- 0.001176732486065166</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.0035809411068362775 +/- 0.0007990529742527231</t>
+          <t>-0.0013909440662917994 +/- 0.0012061369560411417</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.0017756732761171623 +/- 0.0009451742777550177</t>
+          <t>-0.0020124297129328283 +/- 0.0011970256535162504</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>2.9594554601952706e-05 +/- 0.0001593715539252562</t>
+          <t>-0.000503107428233196 +/- 0.00013561928662195197</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.0006806747558449122 +/- 0.00039815401145526687</t>
+          <t>0.00011837821840781082 +/- 0.00019630806690472565</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.0003551346552234325 +/- 0.0005260843099920349</t>
+          <t>-0.0014797277300976463 +/- 0.0005769040748629225</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2156,12 +2156,12 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.0007990529742527231 +/- 0.0005302300345418347</t>
+          <t>-5.918910920390541e-05 +/- 0.0005889242007141769</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.0021899970405445 +/- 0.0006902576969334353</t>
+          <t>0.0019236460491269369 +/- 0.0015046728403534922</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
@@ -2171,37 +2171,37 @@
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>5.918910920390541e-05 +/- 0.0004349493476383191</t>
+          <t>-0.0005918910920390541 +/- 0.0004185302049047261</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.002604320804971838 +/- 0.000905419268468664</t>
+          <t>-0.0004735128736312544 +/- 0.001214458983645055</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.0027522935779816017 +/- 0.0013435406289216882</t>
+          <t>-0.00017756732761172733 +/- 0.001337988109553987</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.00011837821840781082 +/- 0.0006510802012429594</t>
+          <t>-8.878366380585812e-05 +/- 0.0006354220347316809</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>-0.00017756732761172733 +/- 0.0007963080229105518</t>
+          <t>0.001509322284699599 +/- 0.0015740853680937758</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.0026635099141757547 +/- 0.0022264862827823763</t>
+          <t>-0.00224918614974845 +/- 0.0011553253208608186</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>-0.0005622965374371236 +/- 0.0005684928296034155</t>
+          <t>-0.00011837821840781082 +/- 0.0007625983265300321</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>-0.0039881831610045215 +/- 0.0011686877663132868</t>
+          <t>-0.0011225997045790192 +/- 0.0011272545954705356</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2221,157 +2221,157 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.0018316100443131367 +/- 0.0010552774652580004</t>
+          <t>0.0039881831610044105 +/- 0.0011073361780792445</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>-0.0012998522895126042 +/- 0.0010749427118854377</t>
+          <t>-0.0024224519940915677 +/- 0.000525151811953651</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.0018316100443131367 +/- 0.000894106112284873</t>
+          <t>-8.862629246676468e-05 +/- 0.0008041747467542764</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.0023042836041359703 +/- 0.0008122733875845222</t>
+          <t>-0.0006794682422451958 +/- 0.0008149550501703782</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.0012998522895125819 +/- 0.0012266197631921568</t>
+          <t>0.0033382570162481364 +/- 0.0009713017561461454</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0001321162763663089</t>
+          <t>0.0008271787296898036 +/- 0.0007090103397341174</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-0.0009158050221565794 +/- 0.0004845264244270991</t>
+          <t>-0.002511078286558344 +/- 0.0013489453538352697</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.02951255539143275 +/- 0.0027664088292134494</t>
+          <t>0.014387001477104821 +/- 0.002710960318407971</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.019615952732643993 +/- 0.0015017152173871953</t>
+          <t>0.016366322008862576 +/- 0.002004513495265899</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>-0.00047267355982275603 +/- 0.00079489654635592</t>
+          <t>-0.0011816838995568624 +/- 0.0004381801174059453</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>-0.0027769571639587043 +/- 0.0009360696908570528</t>
+          <t>0.002156573116691274 +/- 0.0012948069128987305</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-0.004135893648449107 +/- 0.0017872358596460192</t>
+          <t>-0.004017725258493388 +/- 0.0015699060863322632</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-0.010871491875923244 +/- 0.0017417315182255359</t>
+          <t>-0.017872968980797654 +/- 0.0019202363367799014</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.0040472673559822534 +/- 0.001529641768508071</t>
+          <t>0.005790251107828626 +/- 0.0013290661009396673</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>-0.0004135893648449129 +/- 0.0008582475064303794</t>
+          <t>0.001152141802067941 +/- 0.001206895020136803</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.0012998522895126042 +/- 0.001033551295984435</t>
+          <t>-0.0009453471196454899 +/- 0.001063515509601176</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.00047267355982272274 +/- 0.0018411150902077472</t>
+          <t>0.000738552437223039 +/- 0.001393497951559314</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.954209748892156e-05 +/- 0.0008607859547612046</t>
+          <t>0.001063515509601176 +/- 0.0013486218269439607</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.00023633677991137249 +/- 0.00022107281458043853</t>
+          <t>2.954209748892156e-05 +/- 0.0003840472673559803</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.0015066469719349994 +/- 0.001068836189963099</t>
+          <t>-0.0059084194977844 +/- 0.0013729926190395904</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>-0.0006499261447562854 +/- 0.0007450233508371511</t>
+          <t>0.0019793205317577443 +/- 0.0012606551428863666</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-0.0008862629246676468 +/- 0.0006054328369843158</t>
+          <t>0.000265878877400294 +/- 0.0007976366322008821</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-0.00073855243722305 +/- 0.0005487201069721572</t>
+          <t>0.0002067946824224509 +/- 0.0006871316602430101</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.0015066469719350439 +/- 0.0013241320431914701</t>
+          <t>-0.0014180206794682348 +/- 0.0015452522104132294</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-5.908419497784312e-05 +/- 0.00028945225911765614</t>
+          <t>8.862629246676468e-05 +/- 0.00029689440535068945</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.008301329394386959 +/- 0.0024591023659269306</t>
+          <t>0.007237813884785782 +/- 0.0016567296771414924</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>-0.003870014771048835 +/- 0.00020679468242245093</t>
+          <t>-0.007267355982274815 +/- 0.0011147983612474512</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.0009453471196454899 +/- 0.0010130829069117965</t>
+          <t>-0.0019793205317577443 +/- 0.0012397125706562586</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0035745937961595086 +/- 0.0008906832160520683</t>
+          <t>0.0025110782865583325 +/- 0.0017034804423442741</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>-0.0007680945347119606 +/- 0.000442145629160877</t>
+          <t>5.908419497784312e-05 +/- 0.0006308465732367064</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.0003840472673559803 +/- 0.0002307311573384524</t>
+          <t>-8.862629246676468e-05 +/- 0.0003507929715520785</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -2381,272 +2381,272 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.0008862629246676468 +/- 0.0010486404342274006</t>
+          <t>0.003426883308714901 +/- 0.001233714210801831</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>-0.00623338257016256 +/- 0.0009748892171344115</t>
+          <t>-0.003220088626292472 +/- 0.0009100692349039753</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>-5.908419497784312e-05 +/- 0.0004341783886764843</t>
+          <t>-0.0002067946824224509 +/- 0.000477267191178831</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
+          <t>0.0015952732644017643 +/- 0.0007260387431281798</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>-0.0015952732644017643 +/- 0.0006632184437413156</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0.0005022156573116666 +/- 0.001806904423441412</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-0.00336779911373708 +/- 0.000805800986527997</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.0025701624815361755 +/- 0.0008255946004420707</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>-0.0012998522895125487 +/- 0.0009904315872520013</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.000265878877400294 +/- 0.000786619022493015</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-8.862629246676468e-05 +/- 0.0012606551428863666</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.0024519940915804896 +/- 0.0008567208271787252</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0.004756277695716371 +/- 0.0004661664353931881</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.002954209748892156 +/- 0.001031861104671958</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>0.0002954209748892156 +/- 0.00045766420634651663</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0.001063515509601176 +/- 0.0004219455496923375</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>0.001270310192023627 +/- 0.001529641768508071</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>0.003013293943869999 +/- 0.0009134194879610178</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>0.003485967503692744 +/- 0.0010469746024619946</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>0.0004431314623338234 +/- 0.00042297846568024454</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>0.0010339734121122546 +/- 0.0006638760725035189</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>2.954209748892156e-05 +/- 8.862629246676468e-05</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>-0.002511078286558344 +/- 0.0008485321486762436</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>-0.0017725258493352936 +/- 0.0007114679219375027</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>0.0001477104874446078 +/- 0.0003794751131067965</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>-0.0006499261447562743 +/- 0.0006308465732367064</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>-0.0018020679468242374 +/- 0.0015204855813835167</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0.0009748892171344114 +/- 0.0004391748522102933</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.0035745937961595086 +/- 0.00116269829566643</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>-0.0010930576070900977 +/- 0.0015634999849216157</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>-0.0003249630723781372 +/- 0.0013758500469358884</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>-0.002511078286558344 +/- 0.000917708984756832</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>-0.00023633677991137249 +/- 0.00025754203506887156</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>0.00047267355982274497 +/- 0.0009636340579202367</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>-0.001004431314623333 +/- 0.0006762495209606818</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>0.00047267355982274497 +/- 0.00046146231467690475</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>-0.002688330871491873 +/- 0.0010356601561570683</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>-0.0031905465288035507 +/- 0.0010798030654355954</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>-0.0002954209748892156 +/- 0.0008960561824580811</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>-0.00017725258493352935 +/- 0.00032896687520413544</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>0.0005612998522895096 +/- 0.00027869959031186274</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>0.0008567208271787252 +/- 0.00042708514903399956</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
           <t>-0.0003249630723781372 +/- 0.0005193026833455495</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>-0.002274741506647049 +/- 0.0008965430372522353</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>0.002747415066469705 +/- 0.0007479461684592082</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>0.0003840472673559803 +/- 0.00043917485221029335</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>-0.0033677991137371576 +/- 0.0011069420381208518</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>-0.0005908419497784422 +/- 0.0006054328369843375</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>-0.0017134416543574948 +/- 0.001216618037339714</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>0.00047267355982274497 +/- 0.0008882302143794876</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>0.00416543574593794 +/- 0.0014256931771951067</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>-0.0015361890694239877 +/- 0.0008438910993847248</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>5.908419497784312e-05 +/- 0.0009038143894108286</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>0.0003545051698670587 +/- 0.00034451709866146357</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>0.0016543574593796072 +/- 0.0006632184437413155</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>-0.004313146233382659 +/- 0.001175760634690239</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-0.004431314623338345 +/- 0.0007355922953021369</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-0.004224519940915894 +/- 0.0009158050221565683</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>-0.0011816838995568845 +/- 0.0003736812596949672</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>0.0009453471196454899 +/- 0.0005415155917229915</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>5.908419497784312e-05 +/- 0.00011816838995568624</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>0.0006203840472673416 +/- 0.0014133971892355476</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>-0.004963072378138933 +/- 0.0005878803173451195</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>0.0011225997045790192 +/- 0.0006308465732367064</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
         <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>0.0018906942392909799 +/- 0.0004007285071270448</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>0.0015657311669128426 +/- 0.0007242334222824933</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>-0.003545051698670698 +/- 0.000803631935523508</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>-0.0005612998522895096 +/- 0.0005193026833455495</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0.002806499261447548 +/- 0.0007954453186313849</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>0.0005022156573116554 +/- 0.0014170971882081637</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>-0.0002658788774003051 +/- 0.0009748892171344285</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>0.0003840472673559803 +/- 0.0007595249708822673</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>-5.908419497784312e-05 +/- 0.00011816838995568624</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>-0.00047267355982274497 +/- 0.0005317577548005881</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>-0.0003545051698670587 +/- 0.0006839490045961693</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>-0.00011816838995568624 +/- 0.0004007285071270448</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>-0.0024224519940916566 +/- 0.0011116624946662984</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>-8.862629246676468e-05 +/- 0.0005125362355361117</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>-0.0007090103397341174 +/- 0.000701585943104157</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>0.00017725258493352935 +/- 0.0003012714631369429</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>0.0005022156573116666 +/- 0.0003507929715520785</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>-0.0005908419497784312 +/- 0.00039634882909892665</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.00034954681140913357</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>-0.0017725258493353601 +/- 0.0008144194240526421</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>2.954209748892156e-05 +/- 8.862629246676468e-05</t>
-        </is>
-      </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.001004431314623333 +/- 0.0004219455496923375</t>
+          <t>0.0004135893648449018 +/- 0.0004800022691069966</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.0008567208271787252 +/- 0.0007409120356859314</t>
+          <t>0.002215657311669117 +/- 0.0010083337173338804</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>-0.0021565731166913404 +/- 0.000915805022156612</t>
+          <t>-0.0023929098966026575 +/- 0.0010013855986220764</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.0002954209748892156 +/- 0.0003963488290989267</t>
+          <t>-2.954209748892156e-05 +/- 0.00042708514903399956</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.0005908419497784312 +/- 0.0009153284126930332</t>
+          <t>-0.002097488921713442 +/- 0.0010606394724381983</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>-0.0008862629246676912 +/- 0.0010894587246432167</t>
+          <t>-0.0024224519940915677 +/- 0.0009690528488541588</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>-0.0011225997045790415 +/- 0.0005082614633408014</t>
+          <t>-0.00023633677991137249 +/- 0.0004341783886764843</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-0.00449970396684426 +/- 0.0014550865278205424</t>
+          <t>-0.0031675547661338065 +/- 0.001075949191556305</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2666,157 +2666,157 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.0032859680284191618 +/- 0.0011948156347312215</t>
+          <t>-0.004884547069271772 +/- 0.0016335559101623928</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-0.004144464179988139 +/- 0.001388518578988562</t>
+          <t>-0.003641207815275327 +/- 0.0012770665843767264</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.004203670811130811 +/- 0.0012263064048080152</t>
+          <t>0.0003848431024274457 +/- 0.0007257342020208045</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.004825340438129056 +/- 0.0013175969854510384</t>
+          <t>-0.0031083481349911345 +/- 0.0012784382996855624</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.005802249851983443 +/- 0.0008182519219115059</t>
+          <t>-0.0035523978685612855 +/- 0.0011388622890273275</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.0002368265245706991 +/- 0.0001776198934280382</t>
+          <t>-0.0002368265245707657 +/- 0.00034523101804887857</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-0.004558910597986965 +/- 0.0013119313088312701</t>
+          <t>-0.004144464179988172 +/- 0.0009267303636766355</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.0026050917702783007 +/- 0.0027028329687420515</t>
+          <t>0.0010657193605683513 +/- 0.0018210250443137662</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.008348134991119038 +/- 0.002234216964370995</t>
+          <t>-0.0034043812907045613 +/- 0.0027460964840454187</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>-0.00725281231497924 +/- 0.0016548756494225865</t>
+          <t>0.001243339253996434 +/- 0.0012263064048080715</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.0006808762581409389 +/- 0.0017665516575293965</t>
+          <t>-0.0027827116637063496 +/- 0.0011856118646832964</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.001154529307282437 +/- 0.0016559344311364152</t>
+          <t>-0.004144464179988183 +/- 0.0011767085206839376</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>-0.007193605683836557 +/- 0.0033098836862494145</t>
+          <t>-0.01394316163410302 +/- 0.0027371463145562836</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>0.008821788040260547 +/- 0.0017453407901697536</t>
+          <t>-0.0023386619301361765 +/- 0.0015745513495526566</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>-0.0050325636471284406 +/- 0.0014442049636057316</t>
+          <t>-0.0018650088809946564 +/- 0.0010344230437925547</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-0.007282415630550576 +/- 0.001163225737382389</t>
+          <t>-0.002901124925991716 +/- 0.0010323028877538493</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.010686796921255159 +/- 0.0011874583256442682</t>
+          <t>-0.008111308466548273 +/- 0.0010441203131171589</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.0012137359384250645 +/- 0.0014649902938612912</t>
+          <t>-0.0022498519834221577 +/- 0.0012433392539964408</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-0.0005032563647128008 +/- 0.000325636471284801</t>
+          <t>-0.00047365304914152027 +/- 0.00032964857091947303</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.011071640023682628 +/- 0.001469469940318617</t>
+          <t>-0.00858496151568976 +/- 0.0011692372799367284</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.0020722320899940637 +/- 0.002308299430386985</t>
+          <t>-0.002930728241563063 +/- 0.001929673000323542</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>0.0030787448194197985 +/- 0.0009095495260945666</t>
+          <t>0.002516281823564248 +/- 0.0011407844208405978</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.002013025458851425 +/- 0.0014060795840186925</t>
+          <t>0.002960331557134399 +/- 0.0011311410997361067</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.001568975725281263 +/- 0.0009459174250249015</t>
+          <t>0.0013617525162818 +/- 0.0014085704266868263</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.0001480165778566911 +/- 0.0007160086810211828</t>
+          <t>0.0005328596802841923 +/- 0.000509314699055226</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>-0.0015097690941385244 +/- 0.001702898403584337</t>
+          <t>0.003848431024274701 +/- 0.0017413192622679327</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>-0.03238602723505031 +/- 0.004255470177872472</t>
+          <t>-0.015719360568383668 +/- 0.0025343273802042143</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>-0.00982830076968617 +/- 0.0014907848800490352</t>
+          <t>-0.0033747779751332253 +/- 0.0017919178153252306</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-0.0015393724097098494 +/- 0.0010657193605684019</t>
+          <t>-0.005772646536412085 +/- 0.0014212674818422423</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>5.551115123125783e-17 +/- 0.0003971701558614112</t>
+          <t>0.0002664298401421017 +/- 0.0002459036075464166</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.00017761989342801598 +/- 0.0005490597096208126</t>
+          <t>0.000473653049141487 +/- 0.0002368265245707296</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2826,272 +2826,272 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>-0.001243339253996445 +/- 0.0014966518247204943</t>
+          <t>0.001716992303137954 +/- 0.0011139661173609683</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>-0.017465956187092912 +/- 0.002577359249221899</t>
+          <t>-0.022380106571936054 +/- 0.002928185439639618</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>0.0013913558318532139 +/- 0.00045956704251808055</t>
+          <t>0.001243339253996456 +/- 0.0004918072150928399</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-0.00017761989342801598 +/- 0.00040155890959888893</t>
+          <t>0.000414446417998815 +/- 0.000818251921911489</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>0.0008880994671403575 +/- 0.001450260356887618</t>
+          <t>-0.004174067495559497 +/- 0.001353036694141678</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>-0.008910597986974512 +/- 0.0016612182174775762</t>
+          <t>-0.0001184132622853995 +/- 0.0011707353424088426</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-0.00029603315571339326 +/- 0.0004390881283064348</t>
+          <t>0.0008880994671403242 +/- 0.00035027115352869175</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.004381290704558882 +/- 0.0011139661173609457</t>
+          <t>-0.0011249259917110789 +/- 0.0015653409196450337</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-0.005831853167554746 +/- 0.00138883411554052</t>
+          <t>-0.009177027827116657 +/- 0.0017663035985999033</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>-0.003552397868561252 +/- 0.0016214403715369102</t>
+          <t>-0.0001184132622853884 +/- 0.0016912796752025917</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-0.0006216696269982003 +/- 0.0014469330266252164</t>
+          <t>-0.0004440497335701732 +/- 0.0017274238556418298</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>-0.0016873889875665738 +/- 0.0011159311323251046</t>
+          <t>-0.00204262877442275 +/- 0.0009215146486840272</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-0.0018946121965659924 +/- 0.001027196659141344</t>
+          <t>-0.002841918294849044 +/- 0.000727543263910277</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>0.0029011249259917383 +/- 0.0007227090358634414</t>
+          <t>-0.0005032563647128452 +/- 0.0008584961515689951</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>0.0007992895204263162 +/- 0.000688555556519409</t>
+          <t>8.880994671403019e-05 +/- 0.00044008492443216036</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>0.00014801657785672439 +/- 0.0007860223829101024</t>
+          <t>0.0002368265245707546 +/- 0.0014550865278205461</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.0035820011841326328 +/- 0.0010034607019939767</t>
+          <t>0.00467732386027232 +/- 0.0021946421542747984</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>0.002486678507992934 +/- 0.0011092358789339854</t>
+          <t>-0.0027827116637063496 +/- 0.0016386444645468258</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.004440497335701621 +/- 0.002293062964006754</t>
+          <t>0.001213735938425109 +/- 0.0015004530370010879</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-0.001716992303137932 +/- 0.0006853663056714281</t>
+          <t>0.0007400828892835775 +/- 0.0005169996801827409</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>-0.000888099467140302 +/- 0.0004953582158283577</t>
+          <t>-0.0002960331557134599 +/- 0.0007719600242987408</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>-0.0025458851391355506 +/- 0.0006237805655922476</t>
+          <t>8.880994671400799e-05 +/- 0.0004782561995679039</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.0030491415038484517 +/- 0.0016324826144419487</t>
+          <t>0.0020426287744227055 +/- 0.002205198646117662</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.010479573712255797 +/- 0.0017968017650081243</t>
+          <t>0.0019242155121373616 +/- 0.0018356442863146877</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
+          <t>5.92066311426942e-05 +/- 0.00011841326228538841</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>0.0001776198934280493 +/- 0.000880169848864338</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>0.0002072232089994075 +/- 0.0015611363970911992</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>0.0019242155121373505 +/- 0.001178568930573963</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>0.0010361160449970375 +/- 0.001093721326341677</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.003937240970988742 +/- 0.0014323233159742954</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>0.004174067495559497 +/- 0.00191142077647813</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-0.0002072232089994186 +/- 0.001462595539021384</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>0.002457075192421532 +/- 0.0009911586170978737</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>-0.0002368265245707768 +/- 0.0004144464179988198</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>-0.0009473060982830295 +/- 0.0012615320161434168</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>-0.0016577856719952933 +/- 0.0011480591728635387</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>-0.0010657193605683845 +/- 0.0008288928359976355</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>-0.003285968028419206 +/- 0.001650633731136852</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>-0.0032267613972764785 +/- 0.001943249666344155</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>-0.0035523978685612855 +/- 0.0013948157477074825</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>0.0003848431024274679 +/- 0.00026642984014207705</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>-8.88099467140413e-05 +/- 0.00079489174553568</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>0.0017761989342806373 +/- 0.0006750594583180094</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>8.88099467140746e-05 +/- 0.0007257342020207923</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>-5.9206631142660895e-05 +/- 0.00126845975640194</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>0.0008880994671403575 +/- 0.0013501189166360286</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>-0.00127294256956777 +/- 0.0004595670425180584</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0.0017465956187093345 +/- 0.0007305484120339417</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>0.004262877442273561 +/- 0.00157872014517152</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>-0.0008880994671402909 +/- 0.0011233668419781079</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>0.0021906453522794857 +/- 0.0017118806743399574</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>0.0002368265245707546 +/- 0.0003452310180488576</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>-0.005624629958555338 +/- 0.0009267303636766427</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>-0.003374777975133192 +/- 0.0019645541767953855</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>-0.00047365304914146476 +/- 0.0006095695761389616</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>0.0052397868561279036 +/- 0.0020934798351968384</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>-0.008200118413262259 +/- 0.000783789360264877</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>-0.0015689757252812186 +/- 0.0011620951110947726</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>-5.9206631142660895e-05 +/- 0.0003697452929779984</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>0.0001480165778567577 +/- 0.0010937213263416709</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>5.551115123125783e-17 +/- 0.0006066874343374473</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>-0.0010657193605683624 +/- 0.0006237805655922318</t>
+          <t>8.880994671403019e-05 +/- 0.000592805932341654</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>0.002427471876850229 +/- 0.0014848947547643008</t>
+          <t>-0.004588513913558334 +/- 0.0010361160449970565</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-2.96033155713471e-05 +/- 0.00015941873318931526</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.0002664298401421239 +/- 0.0004479794538313102</t>
+          <t>0.000858496151568966 +/- 0.0005986900063989686</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>-0.0026642984014209614 +/- 0.0009454540806791762</t>
+          <t>-0.0007104795737122638 +/- 0.0011707353424088279</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>0.0037004144464180323 +/- 0.001584538033282726</t>
+          <t>0.0022498519834221243 +/- 0.001787020517795921</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>8.88099467140635e-05 +/- 0.0004782561995678867</t>
+          <t>-0.0003256364712847959 +/- 0.0006411014750653471</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>0.0001480165778567466 +/- 0.001229518037732098</t>
+          <t>0.00082889283599763 +/- 0.0013159331421487904</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>0.005772646536412118 +/- 0.0019468541204804405</t>
+          <t>-0.009088217880402616 +/- 0.0017213252528249514</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>-0.0020130254588513695 +/- 0.0008761781282977399</t>
+          <t>-0.0017465956187093013 +/- 0.0009588001622677141</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>-0.003823252898777829 +/- 0.0005570789355885778</t>
+          <t>-0.0012848636790974588 +/- 0.0010529801075782816</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3111,157 +3111,157 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-3.133813851456946e-05 +/- 0.001098624139326761</t>
+          <t>0.0014728925101849088 +/- 0.0011645818975908441</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.0034158570980883595 +/- 0.0012879174295226962</t>
+          <t>0.0035098715136321124 +/- 0.0017660924855663319</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-0.001880288310874334 +/- 0.0010765004097347218</t>
+          <t>-0.0003133813851457168 +/- 0.0016343973438302016</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.0005014102162331335 +/- 0.0011908492635537323</t>
+          <t>0.0005014102162331669 +/- 0.0013011933244767642</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.006894390473205903 +/- 0.0010673385375071292</t>
+          <t>-0.005421497963020971 +/- 0.0026813802069109507</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.000313381385145739 +/- 0.00042044524804133094</t>
+          <t>-0.00018802883108741674 +/- 0.00028721878376405106</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-0.002507051081165801 +/- 0.0008408904960826412</t>
+          <t>-0.0019116264493888925 +/- 0.0011595111250391557</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>-0.0051081165778752765 +/- 0.0019970534586468</t>
+          <t>0.0011281729865246005 +/- 0.0022476240773476788</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.019931056095267942 +/- 0.004160307558828217</t>
+          <t>0.0066750235036039055 +/- 0.0028689376910462664</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>0.0004700720777185641 +/- 0.0010787787200287192</t>
+          <t>0.005108116577875299 +/- 0.0018168013839718908</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>-0.0010028204324663225 +/- 0.0013859820988715735</t>
+          <t>-0.0012848636790974478 +/- 0.0012092623868113304</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-0.00025070510811658897 +/- 0.0013206711065939013</t>
+          <t>0.0052021309934189965 +/- 0.0018013297227452104</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-0.006298965841429016 +/- 0.0015188493658480115</t>
+          <t>0.005452836101535574 +/- 0.0017061306911709314</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.003165151989971804 +/- 0.0015123696035115697</t>
+          <t>0.009808837355061129 +/- 0.002336951198684076</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>-0.0041679724224381156 +/- 0.0013225288527739705</t>
+          <t>-0.0006894390473205836 +/- 0.0012905835338122289</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-0.004512691946098424 +/- 0.0009422310484721281</t>
+          <t>-0.002287684111563759 +/- 0.0009195487778828574</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-0.003917267314321538 +/- 0.0011994772302729422</t>
+          <t>0.0020369790034472034 +/- 0.0016117067841584308</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>-0.003697900344719551 +/- 0.00087297952223028</t>
+          <t>-0.0014102162331557366 +/- 0.001239739294569253</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-0.0007207771858351753 +/- 0.0003721197770930125</t>
+          <t>-0.00040739580068943626 +/- 0.00042161153391018057</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.00025070510811658897 +/- 0.001990896919369294</t>
+          <t>0.00357254779066124 +/- 0.0017346728302222597</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.002005640864932623 +/- 0.0008195986731821948</t>
+          <t>0.005860231902225022 +/- 0.0014157764961549915</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>0.0003760576621748557 +/- 0.0007521153243497253</t>
+          <t>0.0006267627702914669 +/- 0.001541632576151526</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.0009714822939517198 +/- 0.0008461297398934428</t>
+          <t>0.0021623315575054923 +/- 0.0010805979097190113</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.002726418050767765 +/- 0.0010207770275714454</t>
+          <t>0.0022250078345346313 +/- 0.0012879174295226817</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.00018802883108745005 +/- 0.0005091844816443696</t>
+          <t>0.00034471952366028625 +/- 0.00035593283270450414</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>0.0017549357568160339 +/- 0.001239343148435296</t>
+          <t>0.005327483547477285 +/- 0.0015159369003381917</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1.1102230246251566e-17 +/- 0.0010202958693888726</t>
+          <t>0.008994045753682244 +/- 0.0014295825418937183</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>-0.0002507051081166001 +/- 0.0006979334832754719</t>
+          <t>-0.003321842682544629 +/- 0.0011053081848040472</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-0.002632403635224079 +/- 0.0012072303531343266</t>
+          <t>0.005452836101535574 +/- 0.0007173627792077529</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>-0.00028204324663113625 +/- 0.00016876104064978846</t>
+          <t>-0.00015669069257283618 +/- 0.0008081351901114144</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.0005327483547477363 +/- 0.0003149443942689309</t>
+          <t>0.0007207771858351753 +/- 0.0008057010424432674</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -3271,122 +3271,122 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>-0.0011281729865245892 +/- 0.0007701789863644276</t>
+          <t>-0.001692259479786895 +/- 0.0011990677824950914</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>-0.0001566906925728806 +/- 0.0007315962099610619</t>
+          <t>0.0020996552804763537 +/- 0.001181327284548465</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>3.1338138514558354e-05 +/- 0.0003559328327044875</t>
+          <t>0.0001566906925728806 +/- 0.0005290486686347227</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.0002193669696019973 +/- 0.00039763640051548226</t>
+          <t>0.0005014102162331779 +/- 0.0007952728010309916</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>0.0025070510811657453 +/- 0.0007547223176930278</t>
+          <t>0.0034471952366029734 +/- 0.0011123935662362158</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>-0.0007834534628643142 +/- 0.0007315962099610618</t>
+          <t>-0.0025070510811657453 +/- 0.0009810389120964238</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-0.0012535255405829115 +/- 0.0005605936640551086</t>
+          <t>0.0009088060169226031 +/- 0.0004308281756461153</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.0027577561892823455 +/- 0.0011368446974125486</t>
+          <t>0.0042933249764963936 +/- 0.0010677984981134992</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.0008774678784080004 +/- 0.0008267568761061169</t>
+          <t>-0.0025697273581949064 +/- 0.001212101510862652</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>-0.0017549357568160673 +/- 0.0009211493861923608</t>
+          <t>0.00952679410842997 +/- 0.001041256516818286</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-0.0012535255405829004 +/- 0.0013221575123615746</t>
+          <t>0.003541209652146671 +/- 0.001387752417767773</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.00025070510811657786 +/- 0.0010562393949453284</t>
+          <t>0.0029457850203698068 +/- 0.0013674349250561934</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>9.401441554370837e-05 +/- 0.0011645818975908537</t>
+          <t>-0.000595424631776853 +/- 0.0007983540710032505</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>-0.0020369790034472255 +/- 0.0011829887864730185</t>
+          <t>-0.0003133813851456946 +/- 0.0012921045520581757</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-0.00018802883108743896 +/- 0.0002507051081165945</t>
+          <t>6.267627702917222e-05 +/- 0.0005014102162331557</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>-0.002632403635224079 +/- 0.001002820432466317</t>
+          <t>0.0015042306486994894 +/- 0.0008841576922385461</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>-0.0006267627702914669 +/- 0.0008408904960826453</t>
+          <t>0.003666562206204982 +/- 0.0016226378522093006</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-0.004920087746787849 +/- 0.0010677984981134953</t>
+          <t>-3.1338138514558354e-05 +/- 0.0015821880991995331</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-0.004638044500156702 +/- 0.000968951728846155</t>
+          <t>-0.0036038859291757873 +/- 0.0009322767020146486</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-0.00012535255405830004 +/- 0.0004250911929254288</t>
+          <t>-0.0010654967094954504 +/- 0.0005812358818862699</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>-0.0008147916013789058 +/- 0.00044759814657114786</t>
+          <t>0.0020369790034472147 +/- 0.0004025456778021026</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>-0.0022876841115637703 +/- 0.0005786958731626322</t>
+          <t>0.0011281729865246226 +/- 0.000564086493262302</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>-0.004920087746787838 +/- 0.0017451151102884203</t>
+          <t>0.0015669069257286394 +/- 0.0017672042845342216</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>-0.002319022250078362 +/- 0.001174239673782203</t>
+          <t>-0.0031964901284863402 +/- 0.0014685521170617422</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3396,147 +3396,147 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-0.0006894390473206169 +/- 0.00027319955772740675</t>
+          <t>-0.0011908492635537393 +/- 0.0003914132245940609</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-0.000564086493262328 +/- 0.0008841576922385563</t>
+          <t>-0.001159511125039181 +/- 0.0013806575225265199</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-0.0035098715136320903 +/- 0.0014483509881907115</t>
+          <t>0.0044186775305547045 +/- 0.001459496210867449</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>-0.00021936696960201952 +/- 0.00042161153391017894</t>
+          <t>0.00025070510811658897 +/- 0.0004157473883240881</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-0.0011908492635537616 +/- 0.0012121015108626637</t>
+          <t>-0.004293324976496382 +/- 0.0015797033107024102</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-0.0010028204324663338 +/- 0.0011106264585816032</t>
+          <t>-0.0034785333751174764 +/- 0.0012333856881325154</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-0.0015042306486994783 +/- 0.0009790347447078162</t>
+          <t>0.00031338138514572786 +/- 0.0016283774436561082</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>-0.003102475712942665 +/- 0.0009131182879557184</t>
+          <t>0.00141021623315577 +/- 0.001746240265215289</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>-0.00031338138514572786 +/- 0.000313381385145739</t>
+          <t>-0.00012535255405828893 +/- 0.00040132398855735764</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>-0.0054528361015355855 +/- 0.0011573917463252481</t>
+          <t>-0.002225007834534598 +/- 0.001225397354811483</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>-0.0030084612973989566 +/- 0.0007035394647647737</t>
+          <t>-0.0017549357568160228 +/- 0.001165846144640456</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>-0.0011908492635537616 +/- 0.0006837174625280838</t>
+          <t>0.001159511125039181 +/- 0.0006581009088060432</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>-0.004073958006894407 +/- 0.000829129210612526</t>
+          <t>-0.0034785333751175098 +/- 0.001719033300144452</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>0.000846129739893442 +/- 0.0005954246317768886</t>
+          <t>0.006361642118458177 +/- 0.0012539172061261322</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>-0.009777499216546559 +/- 0.0012281991815898177</t>
+          <t>-0.00567220307113755 +/- 0.0007342760585308667</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>6.267627702913892e-05 +/- 0.00018802883108741676</t>
+          <t>0.0001566906925728584 +/- 0.0003503710400344328</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>-0.002444374804136651 +/- 0.0007255303605634777</t>
+          <t>0.0005014102162331779 +/- 0.0007828264491881405</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>0.00047007207771857515 +/- 0.0004905194560482102</t>
+          <t>0.0008147916013789058 +/- 0.0004895173723538935</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
+          <t>0.0001566906925728473 +/- 0.0001566906925728473</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>0.0017549357568160562 +/- 0.0007309247126098608</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>0.003917267314321538 +/- 0.0010226993965578653</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>-0.000564086493262328 +/- 0.00033752208129957697</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>-0.0007521153243497336 +/- 0.0019429645879034776</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>-0.0015042306486995004 +/- 0.0006837174625281031</t>
+          <t>-0.0006894390473205836 +/- 0.0008501823858508419</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>-0.0019743027264180536 +/- 0.0010207770275714322</t>
+          <t>0.006894390473205891 +/- 0.0013147086783706226</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>-0.0015669069257286284 +/- 0.0005605936640550961</t>
+          <t>0.004136634283923557 +/- 0.000948464177400286</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>-0.001347539956126631 +/- 0.0005954246317768612</t>
+          <t>-0.000908806016922592 +/- 0.0005854447412180887</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>-0.0012535255405828893 +/- 0.0008408904960826619</t>
+          <t>0.001034158570980892 +/- 0.0005786958731626003</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>-0.005515512378564724 +/- 0.0007573203367969039</t>
+          <t>0.0031338138514572346 +/- 0.0008524895336092349</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>-0.0034471952366029734 +/- 0.0009296394217606448</t>
+          <t>0.001034158570980903 +/- 0.0012617249852207774</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.0079563182527301 +/- 0.0011357425724306557</t>
+          <t>-0.004617784711388429 +/- 0.0008912859193189377</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3556,157 +3556,157 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-0.0028705148205927953 +/- 0.00208745443790051</t>
+          <t>0.0034633385335413602 +/- 0.002303193202366383</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-0.002558502340093571 +/- 0.0012068068396763568</t>
+          <t>-0.010920436817472668 +/- 0.002396613337868518</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.007457098283931374 +/- 0.0016299479421665018</t>
+          <t>0.0035257410296412163 +/- 0.0018723348753419671</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.006489859594383807 +/- 0.0018762304372384093</t>
+          <t>0.006552262090483674 +/- 0.0013528538776086643</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.014695787831513273 +/- 0.002760737488701863</t>
+          <t>-0.00424336973478937 +/- 0.0017383323902881893</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.00046801872074885286 +/- 0.0004883767813572167</t>
+          <t>0.0004992199687987809 +/- 0.00037441497659906713</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.004648985959438401 +/- 0.0008764163435374956</t>
+          <t>-0.006583463338533491 +/- 0.0014992840907000265</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.013166926677067115 +/- 0.0032747935758881694</t>
+          <t>0.005522620904836228 +/- 0.002734518391838435</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.021154446177847154 +/- 0.004440673166841127</t>
+          <t>0.011294851794071803 +/- 0.004152931827014012</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>-0.004461778471138833 +/- 0.001603452749769696</t>
+          <t>-0.00636505460218405 +/- 0.0020182167399433793</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-0.0035569422776910776 +/- 0.0015041461208354328</t>
+          <t>-0.004960998439937558 +/- 0.002127412659435965</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.002152886115444641 +/- 0.002513395615993296</t>
+          <t>-0.005304212168486699 +/- 0.002175154453408235</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.026801872074883014 +/- 0.0029184427236125087</t>
+          <t>0.012511700468018772 +/- 0.0030200809619160647</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.01394695787831517 +/- 0.001709247541316987</t>
+          <t>0.01098283931357259 +/- 0.0025108766975014967</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.008923556942277722 +/- 0.001788024808972767</t>
+          <t>-0.002683307332293261 +/- 0.002348191915410523</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-0.0029641185647425795 +/- 0.001478359780403374</t>
+          <t>-0.005647425897035841 +/- 0.0012515551401018053</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>-0.002059282371294835 +/- 0.0011004800055256256</t>
+          <t>-0.0038689547581902905 +/- 0.000895644311663477</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.0005304212168487088 +/- 0.0015973698266671084</t>
+          <t>-0.0014040561622464698 +/- 0.0016524883216056524</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-0.00046801872074880846 +/- 0.0005079195193790877</t>
+          <t>-0.00012480499219966746 +/- 0.00031819154530999334</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.009141965678627184 +/- 0.0016155498865522216</t>
+          <t>0.010826833073322972 +/- 0.0017262497589545208</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>-0.0023088923556942144 +/- 0.0014311818959350455</t>
+          <t>-0.006864274570982809 +/- 0.0013089658011483966</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.005678627145085835 +/- 0.0016498351408926353</t>
+          <t>0.0008112324492980272 +/- 0.001431181895935072</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>-0.0005304212168486422 +/- 0.0011678606722129727</t>
+          <t>0.0033697347893916207 +/- 0.0015399641409364045</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.0015600624024961097 +/- 0.0012402250804587588</t>
+          <t>0.001435257410296431 +/- 0.0014846024653192415</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.0005616224648986145 +/- 0.000748829953198125</t>
+          <t>0.0008424336973479329 +/- 0.0012007414293225794</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.004867394695787852 +/- 0.0013614617303757384</t>
+          <t>0.014414976599064 +/- 0.0031659659017699276</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-0.010202808112324458 +/- 0.0017707910918767647</t>
+          <t>-0.006739469578783108 +/- 0.0009787449074170537</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>-0.010733229329173144 +/- 0.0021535642966286923</t>
+          <t>-0.00424336973478937 +/- 0.0014514450358331205</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-0.013291731669266737 +/- 0.001529815996521848</t>
+          <t>-0.009079563182527273 +/- 0.0010105544299969698</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.00040561622464903025 +/- 0.0006699192060400677</t>
+          <t>-0.0003744149765990357 +/- 0.0005546455174611837</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.00037441497659910226 +/- 0.00033604772587424696</t>
+          <t>0.0002808112324493295 +/- 0.0005993564028798393</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -3716,122 +3716,122 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.012792511700467978 +/- 0.00180320540116067</t>
+          <t>-0.0020904836193447406 +/- 0.0016805283007170217</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.005148205928237082 +/- 0.0017386123826215296</t>
+          <t>-0.0036193447737909224 +/- 0.0020939733835335502</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>0.0016224648985959655 +/- 0.0005887039707991484</t>
+          <t>0.0028081123244930286 +/- 0.000966735312625875</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>0.00024960998439940154 +/- 0.0007991418705064565</t>
+          <t>-0.0005304212168486311 +/- 0.0008021815995121632</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.0037753510140405844 +/- 0.001531406076980725</t>
+          <t>0.0013728549141966196 +/- 0.0013398384120801299</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>-0.008549141965678608 +/- 0.0006864274570983022</t>
+          <t>-0.004867394695787808 +/- 0.0011856474258970307</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>0.001903276131045273 +/- 0.0004056162246489696</t>
+          <t>0.0002808112324493406 +/- 0.0009509984807568167</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.005397815912636539 +/- 0.0016215646128157782</t>
+          <t>0.0006864274570983264 +/- 0.0012773472380941417</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.007737909516380625 +/- 0.0013799278868952326</t>
+          <t>-0.005491419656786245 +/- 0.0017771021361495316</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>-0.0035881435257410165 +/- 0.0017773760210453924</t>
+          <t>-0.0008112324492979383 +/- 0.0024733754986092393</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>0.0005304212168486977 +/- 0.0013887184451961201</t>
+          <t>-0.010577223088923527 +/- 0.0014730822632278051</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>0.0031201248049922193 +/- 0.0020172517785016705</t>
+          <t>0.013322932917316732 +/- 0.0029568841842617538</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.002215288611544475 +/- 0.0009911001668810352</t>
+          <t>-0.0025273010920436544 +/- 0.0011114828786619043</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0.003619344773790978 +/- 0.0020564439380073643</t>
+          <t>-0.0024960998439937155 +/- 0.0016212644064607172</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>0.0019344773790951676 +/- 0.0006515011862034614</t>
+          <t>0.0006864274570983042 +/- 0.0007743946112942818</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>0.0004992199687987919 +/- 0.0010460564501866111</t>
+          <t>0.0018408736349454391 +/- 0.0012973867635751484</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>0.0030577223088923745 +/- 0.0019019969615136718</t>
+          <t>0.0004680187207488751 +/- 0.0013474460456592322</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-0.004024960998439908 +/- 0.000950998480756849</t>
+          <t>-0.010390015600624003 +/- 0.001395711029413107</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-0.004243369734789349 +/- 0.001749497131841032</t>
+          <t>-0.010296411856474208 +/- 0.0014092467757424335</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-0.0005928237129485092 +/- 0.0004289462428975911</t>
+          <t>0.0030889235569423134 +/- 0.0004923473896430308</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.0009360374414976835 +/- 0.0006835850951702733</t>
+          <t>-0.0002496099843993571 +/- 0.0004992199687987627</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0.00015600624024963983 +/- 0.00025155250384707544</t>
+          <t>0.00015600624024965094 +/- 0.00020930433486739025</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-0.009391575663026498 +/- 0.0013270621103361475</t>
+          <t>-0.01207488299531977 +/- 0.00169207449147661</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.005647425897035841 +/- 0.0015628679920584173</t>
+          <t>0.0070202808112324825 +/- 0.0020988493053157088</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3841,92 +3841,92 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>0.00037441497659910226 +/- 0.0003897034632385984</t>
+          <t>0.001154446177847157 +/- 0.0005230282250933136</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>0.005803432137285525 +/- 0.001431181895935064</t>
+          <t>5.551115123125783e-17 +/- 0.000946380710646061</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-0.00377535101404054 +/- 0.0017564390571029591</t>
+          <t>-0.0034633385335413047 +/- 0.001084888527345646</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.0026833073322933164 +/- 0.0009586453351473871</t>
+          <t>0.0017784711388456054 +/- 0.0005590163141082312</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.01082683307332295 +/- 0.0018671281498130535</t>
+          <t>0.0016224648985959877 +/- 0.001462137224818718</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-0.009422776911076413 +/- 0.0008578924857951516</t>
+          <t>-0.010764430577223049 +/- 0.0010557831086232992</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-0.009890795631825244 +/- 0.0018930185724951674</t>
+          <t>6.240249609986703e-05 +/- 0.0022663363241603595</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>0.002215288611544475 +/- 0.0009509984807568268</t>
+          <t>0.00012480499219972297 +/- 0.0008624196543579089</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>-0.0003432137285491299 +/- 0.0004289462428975975</t>
+          <t>-0.0006240249609984261 +/- 0.00019733401935528372</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>0.008892355694227805 +/- 0.0011009222317864148</t>
+          <t>-6.240249609978932e-05 +/- 0.0017135139117311743</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.0026521060842433887 +/- 0.0011778212847536318</t>
+          <t>-0.002028081123244885 +/- 0.0009692495829646643</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.0012480499219969076 +/- 0.0007514255587389897</t>
+          <t>6.240249609987814e-05 +/- 0.0007488299531981351</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.009204368174726996 +/- 0.0019144959696277485</t>
+          <t>0.013042121684867448 +/- 0.0016790794442525974</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>0.0042121684867395095 +/- 0.0015364832764112484</t>
+          <t>0.0024024960998440315 +/- 0.0013093376136260166</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>0.00608424336973481 +/- 0.000780031201248037</t>
+          <t>0.014383775351014084 +/- 0.0012437523512009118</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>-0.0001872074882995123 +/- 0.00028596416193172794</t>
+          <t>-0.00031201248049919086 +/- 0.00044125228155167363</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>0.0012792511700468357 +/- 0.0003257505931017413</t>
+          <t>0.0018408736349454613 +/- 0.0007039322416647975</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>0.001216848673947002 +/- 0.0006899639434476154</t>
+          <t>-0.0008736349453978054 +/- 0.0007223611171787858</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3936,12 +3936,12 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>-0.0005928237129484981 +/- 0.0003543780559001803</t>
+          <t>0.00230889235569427 +/- 0.000727731905752941</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>0.0004368174726989471 +/- 0.0014911454783586259</t>
+          <t>0.012230889235569475 +/- 0.0016848673946958084</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -3951,37 +3951,37 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>-0.00012480499219965635 +/- 0.00039957093525322694</t>
+          <t>0.00024960998439940154 +/- 0.0006662763339801136</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>0.003962558502340108 +/- 0.00138871844519611</t>
+          <t>0.0029329173166926957 +/- 0.0014714291572607244</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>0.0037753510140405844 +/- 0.001348890254054123</t>
+          <t>0.0030889235569423134 +/- 0.0009509984807568134</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>0.0006240249609984816 +/- 0.0006691922180819711</t>
+          <t>-0.00018720748829950117 +/- 0.0011691103897157602</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>0.0013416536661466805 +/- 0.0008260968670747854</t>
+          <t>0.004274570982839343 +/- 0.0008607247565762138</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>0.004336973478939165 +/- 0.0012437523512009204</t>
+          <t>0.013510140405616267 +/- 0.0017652848873404747</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>0.0022152886115444858 +/- 0.0008539115247053856</t>
+          <t>0.0007800312012480992 +/- 0.0006581910486655037</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-0.0009725906277630481 +/- 0.0012917540230363333</t>
+          <t>-0.00011788977306221859 +/- 0.0012587183320991856</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4001,157 +4001,157 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.01214264662540523 +/- 0.002408098817072264</t>
+          <t>0.011111111111111082 +/- 0.0015430168125798221</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.008900677866195094 +/- 0.0012350325281318547</t>
+          <t>0.009460654288240467 +/- 0.0015054043960061431</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.0011494252873563316 +/- 0.0016486137661004473</t>
+          <t>0.0033009136457412104 +/- 0.0011090414218819192</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-5.8944886531109296e-05 +/- 0.0017124478687101606</t>
+          <t>0.006867079280872346 +/- 0.0021539093888114686</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.009342764515178303 +/- 0.0018407894452846774</t>
+          <t>-0.004214559386973194 +/- 0.002320849646048929</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.000501031535514318 +/- 0.00029619438906929995</t>
+          <t>0.00014736221632769553 +/- 0.00030200267509459476</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-0.0015325670498084532 +/- 0.0019272363954343508</t>
+          <t>0.008134394341290851 +/- 0.002154514221337693</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.039876215738284704 +/- 0.0013763978106496359</t>
+          <t>0.04002357795461242 +/- 0.003206406783132147</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.035219569702328334 +/- 0.0019382473383386287</t>
+          <t>0.03740053050397875 +/- 0.0019391434305447686</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-0.010138520483348078 +/- 0.002539423428062256</t>
+          <t>-0.005894488653109375 +/- 0.0018168034196784425</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.011494252873563227 +/- 0.0016249983792620307</t>
+          <t>0.017565576186265808 +/- 0.002570024091552207</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.014706749189507828 +/- 0.0016004920698361803</t>
+          <t>0.03418803418803416 +/- 0.0015028056332427803</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.0004126142057176652 +/- 0.0022336923455934443</t>
+          <t>0.001296787503684016 +/- 0.0035835388514165946</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.011199528440907791 +/- 0.0015200467973153766</t>
+          <t>0.023577954612437335 +/- 0.0014134487248195422</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>-0.009932213380489241 +/- 0.001264570465837017</t>
+          <t>0.002475685234305891 +/- 0.0017545388819495732</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-0.0002947244326554577 +/- 0.0014970144531919012</t>
+          <t>0.004921898025346272 +/- 0.002177971681325336</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>-0.0007368110816386552 +/- 0.0018417329560822802</t>
+          <t>0.003743000294724408 +/- 0.002084224840346246</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.0002947244326554577 +/- 0.000941274354416221</t>
+          <t>0.003271441202475667 +/- 0.001359890597708137</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.0004420866489832087 +/- 0.0003785803884074672</t>
+          <t>-0.00038314176245215494 +/- 0.0002961943890692944</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.01579722959033304 +/- 0.002298850574712653</t>
+          <t>-0.011759504862953175 +/- 0.0028890511902354226</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>-0.0055997642204538844 +/- 0.0013376723510651553</t>
+          <t>-0.00586501620984381 +/- 0.002102482384557836</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.00297671676982022 +/- 0.0007030274354185956</t>
+          <t>-0.0017978190391983672 +/- 0.0011674212979863525</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>-0.0012967875036840493 +/- 0.0013259324349191794</t>
+          <t>0.0017683465959327572 +/- 0.001763427680713415</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.003448275862068961 +/- 0.0017137155036966193</t>
+          <t>0.0016799292661361265 +/- 0.0013051334998811957</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.001473622163277366 +/- 0.0007338579191269574</t>
+          <t>-0.00047155909224877446 +/- 0.0006616547103048449</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.0086943707633363 +/- 0.0027307773380250014</t>
+          <t>-0.0005305039787798837 +/- 0.0010445060504962868</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-0.012820512820512808 +/- 0.0024561351783083433</t>
+          <t>-0.0012967875036840825 +/- 0.0025015143146387272</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>-0.012083701738874141 +/- 0.0012573374009844551</t>
+          <t>-0.00020630710285886035 +/- 0.001592875816902059</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-0.0006483937518420135 +/- 0.0012900718319032892</t>
+          <t>0.0025051576775714456 +/- 0.001860502694027302</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>-0.0014146772767462568 +/- 0.0007314868049508245</t>
+          <t>-0.0007662835249042432 +/- 0.0008861359492114749</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.0012967875036840604 +/- 0.0007708044108825339</t>
+          <t>-0.0006778661951075904 +/- 0.0006596825607308853</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -4161,217 +4161,217 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.011258473327438845 +/- 0.002066436562682959</t>
+          <t>0.004126142057176508 +/- 0.002857459391344732</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.00754494547597997 +/- 0.001855594015761524</t>
+          <t>-0.006955496610669065 +/- 0.002532573069135387</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>0.0004715590922487412 +/- 0.0007708044108825074</t>
+          <t>0.0031240789861479157 +/- 0.0007362213968049849</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>-0.0028293545534925023 +/- 0.0013193651214617884</t>
+          <t>-2.9472443265587957e-05 +/- 0.0009725906277630467</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>0.005363984674329492 +/- 0.0016661708252404968</t>
+          <t>0.0014146772767462124 +/- 0.0014366115658065483</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>-0.0044798113763631076 +/- 0.0014122191041215481</t>
+          <t>-0.004980842911877425 +/- 0.0019525354641970814</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-0.001326259946949604 +/- 0.0008151675028552295</t>
+          <t>-0.00044208664898323093 +/- 0.0007368110816386708</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.0006778661951075792 +/- 0.0008236480172403199</t>
+          <t>0.0023872679045092494 +/- 0.001648613766100447</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>-0.0020335985853227267 +/- 0.0011524441376962813</t>
+          <t>-0.0048924255820807835 +/- 0.0012378426171529664</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>-0.0017094017094017144 +/- 0.0008315199516455053</t>
+          <t>0.0051282051282050874 +/- 0.0010395043966135188</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-0.001532567049808431 +/- 0.0015016491839501343</t>
+          <t>0.0020335985853226933 +/- 0.0018567639257294404</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>0.005305039787798405 +/- 0.0011788977306218752</t>
+          <t>0.019451812555260795 +/- 0.0017975774455616727</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>-0.008812260536398464 +/- 0.0010162652313331483</t>
+          <t>-0.001061007957559701 +/- 0.0011043320952075055</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.0024756852343059245 +/- 0.0012656003863002788</t>
+          <t>0.0012673150604184946 +/- 0.001038250218320575</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-0.0028588269967580572 +/- 0.0005901852164603636</t>
+          <t>-0.00044208664898323093 +/- 0.0006217218717868622</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>-0.0005010315355142958 +/- 0.0014441497200117913</t>
+          <t>0.010757441791924515 +/- 0.0016422790115832454</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>-0.006366047745358094 +/- 0.00140234332488892</t>
+          <t>-0.00032419687592102344 +/- 0.0013789198426512996</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-0.00014736221632771773 +/- 0.0012451889286341114</t>
+          <t>0.019127615679339804 +/- 0.002077545953265798</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>0.0042440318302387255 +/- 0.0023914486030180686</t>
+          <t>0.01688770999115824 +/- 0.0016412208420071767</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-0.0004420866489831976 +/- 0.0006490632344693565</t>
+          <t>5.894488653107599e-05 +/- 0.000368110698402488</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>-0.000766283524904221 +/- 0.0008762787354741197</t>
+          <t>-0.00014736221632775104 +/- 0.0008044411473006976</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>8.841732979661954e-05 +/- 0.0002652519893899203</t>
+          <t>0.0009431181844974823 +/- 0.00025693480362751095</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>0.0027409372236958498 +/- 0.0015260351860889518</t>
+          <t>0.01918656056587088 +/- 0.00108248556865352</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.0028293545534924915 +/- 0.0016045573343726684</t>
+          <t>0.007662835249042122 +/- 0.0014438489494743132</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>-2.9472443265543545e-05 +/- 8.841732979663064e-05</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-0.0007662835249041989 +/- 0.0007594517375022197</t>
+          <t>-0.0009431181844975156 +/- 0.0005714918782689573</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-0.0008547008547008406 +/- 0.0009990245362026598</t>
+          <t>0.005658709106984938 +/- 0.0022399056881815395</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-0.0024462127910403917 +/- 0.0017832654886419967</t>
+          <t>0.002799882110226903 +/- 0.0027371316859720963</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.00035366931918655585 +/- 0.0009301346205752691</t>
+          <t>-0.0009431181844975267 +/- 0.0008622893509182167</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-0.0006189213085764922 +/- 0.001121890145044172</t>
+          <t>-0.0015030946065429207 +/- 0.0017157417716272237</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-0.006926024167403478 +/- 0.0009060080252837825</t>
+          <t>0.011435307987032106 +/- 0.0016971623989257677</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-0.004126142057176541 +/- 0.0012504098694722239</t>
+          <t>0.009519599174771543 +/- 0.0017338716274780716</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>-0.00542292956086059 +/- 0.001230805365035141</t>
+          <t>0.003035661656351274 +/- 0.0015030946065428782</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>-0.00020630710285881592 +/- 0.00023018714046290725</t>
+          <t>-2.947244326556575e-05 +/- 0.00024481650052810054</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>-0.015561450044208659 +/- 0.0018630687449783712</t>
+          <t>0.0009725906277630036 +/- 0.0019328620609572317</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>-0.00792808723843207 +/- 0.0010984170441252124</t>
+          <t>-0.0025346301208370448 +/- 0.0014748005898257233</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>-0.00041261420571765407 +/- 0.0006616547103048626</t>
+          <t>-0.005570291777188363 +/- 0.0010162652313331234</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>-0.02272325375773653 +/- 0.0021795663889754473</t>
+          <t>0.008841732979663975 +/- 0.002426783241996932</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>-0.0021220159151193684 +/- 0.0011700225901137222</t>
+          <t>0.00020630710285880484 +/- 0.001821816617804378</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
         <is>
-          <t>-0.0013557323902151364 +/- 0.0011949976382383475</t>
+          <t>0.0023872679045092494 +/- 0.001870745779258291</t>
         </is>
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>-0.0002652519893899252 +/- 0.00027804247368278537</t>
+          <t>0.0006189213085764589 +/- 0.0004051791065389796</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>-0.00480400825228412 +/- 0.0009600057456470596</t>
+          <t>0.0007957559681697312 +/- 0.0008547008547008604</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>-0.003035661656351318 +/- 0.0005599764220453683</t>
+          <t>0.000677866195107546 +/- 0.0010711925638306103</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4381,52 +4381,52 @@
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>-0.003006189213085786 +/- 0.0009207485618516431</t>
+          <t>-0.0018862363689950423 +/- 0.0009522837855233223</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>-0.0019746536987916286 +/- 0.0015203324935489538</t>
+          <t>0.005481874447391644 +/- 0.0014865334763240169</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>-0.004509283819628673 +/- 0.00029619438906930103</t>
+          <t>-0.000854700854700885 +/- 0.0004051791065389594</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>-2.9472443265543545e-05 +/- 0.0006778661951075836</t>
+          <t>-0.0012967875036840938 +/- 0.0010724082168382166</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>-0.005629236663719417 +/- 0.0013275691870975825</t>
+          <t>0.0032714412024756555 +/- 0.0017458536067928064</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>-0.003625110521662256 +/- 0.0013051334998812139</t>
+          <t>0.0046566460359563355 +/- 0.0013167290246795472</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>-0.0013557323902151585 +/- 0.000988096352150903</t>
+          <t>0.0009136457412319277 +/- 0.0012325684448173649</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>-0.014470969643383447 +/- 0.0013662631283818867</t>
+          <t>0.004656646035956347 +/- 0.0015584207564282107</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>-0.01732979664014146 +/- 0.001501649183950133</t>
+          <t>0.005658709106984916 +/- 0.001518903475004434</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>-0.0023872679045092715 +/- 0.00095456143475991</t>
+          <t>0.0009725906277629926 +/- 0.0010711925638306034</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0.0014693171996543407 +/- 0.0009850372225455786</t>
+          <t>-0.0029098242581388377 +/- 0.0008295119590255017</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4446,157 +4446,157 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.0037453183520598787 +/- 0.0012223107712818603</t>
+          <t>-0.004782483434168816 +/- 0.0005932371155855256</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-0.0038605589167386434 +/- 0.0012304325268834666</t>
+          <t>0.0019590895995390545 +/- 0.0012003841346009735</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.00011524056467872023 +/- 0.001605115330127813</t>
+          <t>0.0026505329876116536 +/- 0.00124117886652482</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.004292711034284002 +/- 0.0013167841984473112</t>
+          <t>-0.0039181791990780535 +/- 0.0012767801674537804</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.007778738115816808 +/- 0.0012558049390782714</t>
+          <t>-0.0008354940939210298 +/- 0.0017640183825804237</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.0006050129645635671 +/- 0.000239315006134172</t>
+          <t>-2.8810141169677284e-05 +/- 0.0003007867043765518</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.002189570728896595 +/- 0.0013340059813068644</t>
+          <t>-0.0030826851051570015 +/- 0.001208996557669672</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.0039757994814174965 +/- 0.001816638751994756</t>
+          <t>-0.0035724575050417482 +/- 0.0016858241242671073</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.010515701526937538 +/- 0.002964086118720758</t>
+          <t>-0.0019014693171996444 +/- 0.0026095054737480215</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.0004321521175454146 +/- 0.001146991024914687</t>
+          <t>-0.009132814750792273 +/- 0.0022941629561069863</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>-0.010602131950446503 +/- 0.0019868556208086268</t>
+          <t>-0.01037165082108903 +/- 0.0010779767752157497</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>-0.003543647363872038 +/- 0.0013699214552542434</t>
+          <t>-0.010976663785652551 +/- 0.0013293312584338138</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>-0.007000864304235033 +/- 0.001387979195672258</t>
+          <t>-0.005041774704696045 +/- 0.001579310869912508</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.015759147219821433 +/- 0.002410601514924679</t>
+          <t>0.006741573033707882 +/- 0.0013402135810559478</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.0004321521175454257 +/- 0.0011397315151168224</t>
+          <t>-0.002708153269951008 +/- 0.0012961362004266226</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>8.643042350912067e-05 +/- 0.001256135370590137</t>
+          <t>-0.002765773552290385 +/- 0.001094785364448278</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>-0.0005762028233937788 +/- 0.0013012491835939232</t>
+          <t>-0.006453471622010931 +/- 0.0011393673254557857</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>-0.0033131662345144753 +/- 0.0006601232634623806</t>
+          <t>-0.007346585998271382 +/- 0.0010000895971022591</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2.8810141169732795e-05 +/- 0.00027179432820676977</t>
+          <t>0.0002304811293575293 +/- 0.0004033419763756723</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.0024200518582541465 +/- 0.0014300977984432058</t>
+          <t>-0.003486027081532672 +/- 0.0011117131306006842</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>-0.0005473926822241015 +/- 0.0010890843083512217</t>
+          <t>-0.00423509075194467 +/- 0.0011812157879573428</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.002535292422932911 +/- 0.0006544406045289733</t>
+          <t>0.001238836070296756 +/- 0.0008153829846202912</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.00411985018726595 +/- 0.0007179450184026016</t>
+          <t>0.0021031403053875077 +/- 0.000773593868170433</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.0030538749639873576 +/- 0.0013402135810559592</t>
+          <t>0.005099394987035455 +/- 0.0009816609067934737</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.0007778738115817307 +/- 0.0006185799640905863</t>
+          <t>0.001440507058484608 +/- 0.0006043266195160862</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.008009219245174348 +/- 0.0014847708126447738</t>
+          <t>0.003860558916738699 +/- 0.0017862287525208672</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0.003169115528666133 +/- 0.0011595858137423206</t>
+          <t>-0.0028522039757994722 +/- 0.001877970439381424</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>-0.004782483434168783 +/- 0.0012961362004266232</t>
+          <t>-0.0003457216940362828 +/- 0.001220951892850309</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>-0.00328435609334482 +/- 0.0017954982945413895</t>
+          <t>-0.011639297032555451 +/- 0.0013025242933399285</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.001210025929127112 +/- 0.00033598109448837113</t>
+          <t>0.00028810141169692826 +/- 0.0006694871817126079</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.002218380870066328 +/- 0.0003169115528665894</t>
+          <t>0.00014405070584845304 +/- 0.0003918602854720745</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -4606,122 +4606,122 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>-0.010054739268222378 +/- 0.001042353933455813</t>
+          <t>-0.0057044079515989445 +/- 0.001261081453658268</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.00023048112935747378 +/- 0.0014679042584681138</t>
+          <t>0.0018150388936905904 +/- 0.0022760011524056343</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>-0.002592912705272199 +/- 0.0004990062827913854</t>
+          <t>-0.0007778738115816752 +/- 0.00048294596987151896</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>0.0006050129645635782 +/- 0.0005826490468498068</t>
+          <t>0.000749063670412009 +/- 0.0009219245174301325</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>0.003370786516853985 +/- 0.0014465445359415818</t>
+          <t>0.004494382022471932 +/- 0.001573782804234825</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>0.00034572169403634945 +/- 0.0012676462114664339</t>
+          <t>-0.00011524056467874245 +/- 0.0009037388154052461</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>0.002535292422932922 +/- 0.0006152162634417322</t>
+          <t>-0.0005185825410544354 +/- 0.0007033451809699621</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.0029098242581389157 +/- 0.0009680378920432933</t>
+          <t>0.0014116969173149196 +/- 0.0007339521292340628</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.0033131662345145863 +/- 0.0010000895971022529</t>
+          <t>-0.008988764044943809 +/- 0.0016388893867275145</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>-0.0034284067991932734 +/- 0.001126546516624426</t>
+          <t>-0.0008643042350907293 +/- 0.0008249968921507406</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-0.003313166234514486 +/- 0.0009489869831172847</t>
+          <t>-0.01901469317199652 +/- 0.001417271550129517</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>0.004638432728320407 +/- 0.0012913243924526014</t>
+          <t>0.005963699222126207 +/- 0.0014058050012971523</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>-0.0005473926822241015 +/- 0.0010966791305487905</t>
+          <t>-0.0031403053874963782 +/- 0.000985037222545592</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>-0.004119850187265861 +/- 0.001202111555460969</t>
+          <t>-0.010256410256410253 +/- 0.0018501405195047273</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>0.0011235955056180357 +/- 0.0006992025986466187</t>
+          <t>0.000749063670411998 +/- 0.0004500287914668214</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>0.0016421780466725044 +/- 0.0015193081963048298</t>
+          <t>-0.003601267646211437 +/- 0.0014984043358047688</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>-0.009680207433016364 +/- 0.001640913957464487</t>
+          <t>-0.018726591760299605 +/- 0.0011379094012175916</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-0.0066839527513684275 +/- 0.0010686970320363685</t>
+          <t>-0.01751656583117256 +/- 0.0015288388546726098</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-0.011235955056179725 +/- 0.0012754793213009784</t>
+          <t>-0.005445116681071727 +/- 0.00207932590904824</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>0.0002881014116969616 +/- 0.00022316239390421857</t>
+          <t>0.0006626332469029328 +/- 0.00048294596987151175</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>0.0008066839527514191 +/- 0.0005586493641505608</t>
+          <t>0.0006626332469029328 +/- 0.0006185799640905884</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>-0.0005185825410544021 +/- 0.0003102947166311883</t>
+          <t>1.1102230246251566e-17 +/- 0.0003155992840709523</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-0.012129069432440165 +/- 0.0015803616423972875</t>
+          <t>-0.01610486891385767 +/- 0.0016421780466724402</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-0.0024776721405934342 +/- 0.0011393673254557965</t>
+          <t>-0.01722846441947564 +/- 0.0009537853850329494</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4731,92 +4731,92 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>0.0008354940939211075 +/- 0.000675043187200233</t>
+          <t>0.00034572169403630505 +/- 0.0004786300122683855</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-0.001354076634975443 +/- 0.0008931143762604452</t>
+          <t>-0.006367041198501855 +/- 0.0011042217168963791</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-0.004263900893114325 +/- 0.0016287287842238621</t>
+          <t>-0.0061365600691443145 +/- 0.0012294202416221018</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.00034572169403634945 +/- 0.0007490636704119767</t>
+          <t>0.0013540766349755206 +/- 0.0006823808287137646</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.00031691155286666105 +/- 0.0008875207030106215</t>
+          <t>-0.003370786516853919 +/- 0.0015356102530955276</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-0.00847018150388933 +/- 0.001327769360046427</t>
+          <t>-0.022241428983002 +/- 0.0014102262460985871</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>0.006050129645635294 +/- 0.0018979739662345894</t>
+          <t>0.004840103716508237 +/- 0.0012209518928502931</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>0.0059636992221262395 +/- 0.00130792964135018</t>
+          <t>0.002391241717084447 +/- 0.0011087226392909049</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>-8.643042350903185e-05 +/- 0.0003169115528666116</t>
+          <t>5.762028233939898e-05 +/- 0.000382209713668139</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.012330740420628095 +/- 0.0017936482185276431</t>
+          <t>0.007663497551138021 +/- 0.0016409139574644974</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.010919043503313209 +/- 0.0012977361716571775</t>
+          <t>0.0008931143762604621 +/- 0.0011699187844567483</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.008153269951022802 +/- 0.001557080854724485</t>
+          <t>0.0013828867761452202 +/- 0.0013439243779533793</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0.025151253241140904 +/- 0.0019795313611411024</t>
+          <t>0.00970901757418613 +/- 0.0014693171996542926</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>0.01025641025641032 +/- 0.0013152073996558176</t>
+          <t>0.0043791414577931675 +/- 0.001318988549957889</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>0.016421780466724333 +/- 0.002190328759291067</t>
+          <t>0.012503601267646214 +/- 0.0019248969275125387</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>-0.00011524056467873133 +/- 0.000320816154585414</t>
+          <t>-0.00028810141169689497 +/- 0.00022316239390420423</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>0.0035724575050418263 +/- 0.0006070673438693799</t>
+          <t>0.001008354940939238 +/- 0.0008174163618041558</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>0.0012676462114664777 +/- 0.0008757524721158709</t>
+          <t>0.00014405070584845304 +/- 0.0009223745660375811</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4826,52 +4826,52 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>0.001498127340824018 +/- 0.000641632309170837</t>
+          <t>0.003658887928550869 +/- 0.0012495101378393232</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>0.0033707865168539743 +/- 0.0015193081963048246</t>
+          <t>0.0015557476231633726 +/- 0.0011962281470484957</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>-5.762028233937677e-05 +/- 0.00011524056467875355</t>
+          <t>-0.00028810141169688386 +/- 0.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>0.001411696917314953 +/- 0.0009680378920433048</t>
+          <t>0.0027369634111207297 +/- 0.000913331459760712</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.0058772687986171634 +/- 0.0014531282296650389</t>
+          <t>0.003572457505041793 +/- 0.0011681437587273628</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>0.012849322961682586 +/- 0.001739140106342461</t>
+          <t>0.001498127340824007 +/- 0.0012676462114664232</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>0.007836358398156208 +/- 0.0014903505798187808</t>
+          <t>-0.00043215211754535907 +/- 0.0015687644356164796</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>-0.0002016709881877965 +/- 0.0009205730514935393</t>
+          <t>0.003428406799193329 +/- 0.0010181847909577814</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>0.010400460962258763 +/- 0.0018823850445312186</t>
+          <t>0.009334485738980148 +/- 0.0017769108550975724</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>0.003025064822817669 +/- 0.0009133314597607278</t>
+          <t>0.003572457505041793 +/- 0.0009996745360355665</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0.0013384889946460587 +/- 0.0012982244403804278</t>
+          <t>-0.004550862581796544 +/- 0.0019001399468988058</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4891,157 +4891,157 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.005383700178465201 +/- 0.0011554387031264158</t>
+          <t>-0.011362284354550844 +/- 0.0021357909662125217</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.0013682331945270576 +/- 0.0010320851619808166</t>
+          <t>0.006157049375371826 +/- 0.0013633749716080643</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.0005948839976204878 +/- 0.0013951266388529024</t>
+          <t>0.004461629982153481 +/- 0.0011129260519851046</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.0021118381915526284 +/- 0.001352952458720314</t>
+          <t>-0.005562165377751338 +/- 0.0018434206344255055</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.002974419988102317 +/- 0.0015340626958034182</t>
+          <t>0.008030933967876264 +/- 0.002169492269935812</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.00023795359904817958 +/- 0.00029143245006343975</t>
+          <t>0.00011897679952409535 +/- 0.0003569303985722768</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.0007733491969066142 +/- 0.0019558931853389137</t>
+          <t>0.006335514574657974 +/- 0.001255261620821496</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.018798334324806664 +/- 0.0028862604332440815</t>
+          <t>0.02281380130874482 +/- 0.00266056838474875</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.021743010113027983 +/- 0.0025602483108870104</t>
+          <t>0.023825104104699603 +/- 0.0028759734388430157</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>-0.0025580011897679998 +/- 0.0006267491822042304</t>
+          <t>0.00303390838786437 +/- 0.0021564032076611442</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-0.00496728138013085 +/- 0.0010892226902796168</t>
+          <t>0.003628792385484836 +/- 0.0009002228405961647</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.002201070791195714 +/- 0.0012910490430821258</t>
+          <t>0.012492563950029767 +/- 0.0015166625560954147</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.020582986317668084 +/- 0.002264469519413954</t>
+          <t>0.019512195121951226 +/- 0.0017097094423795414</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.031439619274241534 +/- 0.002488756055414515</t>
+          <t>0.03310529446757884 +/- 0.0028654951467284653</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0.0015169541939321963 +/- 0.0015308874756047228</t>
+          <t>0.007346817370612746 +/- 0.001551552808535986</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-0.0038370017846519723 +/- 0.0015538319912681766</t>
+          <t>-0.0031528851873884435 +/- 0.001324869568787635</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>0.0019928613920285666 +/- 0.001343766448313672</t>
+          <t>0.0010707911957168249 +/- 0.0009330390922878137</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>-0.001992861392028522 +/- 0.0012195121951219582</t>
+          <t>-0.0010410469958358148 +/- 0.0017957714274983332</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2.9744199881021062e-05 +/- 0.0002470738805150945</t>
+          <t>0.00023795359904817958 +/- 0.00045693906887973363</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.0001487209994051275 +/- 0.0020184458747559333</t>
+          <t>0.0017251635930993548 +/- 0.001912901271958784</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>-0.0035990481856037924 +/- 0.0013198517389847707</t>
+          <t>0.0031528851873884657 +/- 0.0011224248818627932</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.0023200475907198203 +/- 0.0009387111146971778</t>
+          <t>0.002290303390838788 +/- 0.0007291880233272609</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.0031826293872694866 +/- 0.0014755641588117213</t>
+          <t>0.002617489589530053 +/- 0.0005117385643689837</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.007674003569304044 +/- 0.001028650592848934</t>
+          <t>0.005681142177275433 +/- 0.001741750859245376</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-0.0016359309934562583 +/- 0.000668417758900784</t>
+          <t>-0.001130279595478878 +/- 0.0005287444626600608</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>0.006603212373587153 +/- 0.0005767614345528062</t>
+          <t>0.011986912552052354 +/- 0.0022926199491425676</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0.0019928613920285666 +/- 0.0021778361104087345</t>
+          <t>0.009339678762641301 +/- 0.001540967739082519</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>-0.0025282569898869454 +/- 0.0008008870920783106</t>
+          <t>0.0038072575847709735 +/- 0.0014252407555872591</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-0.0010707911957168249 +/- 0.000913878137759502</t>
+          <t>0.0019333729922665244 +/- 0.001169140036111438</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>-5.948839976203102e-05 +/- 0.0003468739973138151</t>
+          <t>0.0006841165972635399 +/- 0.0006657652970136635</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.0016359309934562583 +/- 0.000598590475832763</t>
+          <t>-0.0006543723973824967 +/- 0.0004164187983343377</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -5051,272 +5051,272 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.003123140987507422 +/- 0.0009143620552611266</t>
+          <t>0.002290303390838788 +/- 0.0013437664483136847</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.0024092801903629057 +/- 0.001279000594883999</t>
+          <t>0.008417608566329582 +/- 0.0009958756123011742</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>-0.0005056513979773581 +/- 0.0008828567566719746</t>
+          <t>0.0005056513979774136 +/- 0.0008418186613970679</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-0.0005651397977394113 +/- 0.0009633631612553028</t>
+          <t>2.9744199881021062e-05 +/- 0.0008460120555221843</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>0.007079119571683545 +/- 0.0007618232287249119</t>
+          <t>0.0028256989886972115 +/- 0.0026108902258927262</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>0.00041641879833435034 +/- 0.0007063856089849999</t>
+          <t>0.0037477691850089203 +/- 0.0007310056946724779</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-0.0003271861986912317 +/- 0.0008868561282495875</t>
+          <t>-0.0020226055919095654 +/- 0.0008803479230784631</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.0009220701963117306 +/- 0.001042745279176576</t>
+          <t>0.0017846519928613968 +/- 0.0013823854894256034</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>-0.00017846519928611527 +/- 0.001065822300248014</t>
+          <t>0.0007138607971445721 +/- 0.0012633409031288176</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.00303390838786437 +/- 0.0010025163323231939</t>
+          <t>0.005294467578822149 +/- 0.0007847058868693109</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-0.005829863176680517 +/- 0.0012978836543290466</t>
+          <t>-0.007971445568114199 +/- 0.0011192675622978593</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.0024092801903628724 +/- 0.001352952458720306</t>
+          <t>0.002260559190957756 +/- 0.0013963943598221875</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>0.004580606781677566 +/- 0.000904145398784701</t>
+          <t>0.0035693039857227936 +/- 0.001254909167741159</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-0.000475907198096337 +/- 0.0011687616123966793</t>
+          <t>0.007614515169541969 +/- 0.0009518143961927357</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-0.0009518143961927295 +/- 0.0006351622993474913</t>
+          <t>-0.0002379535990481685 +/- 0.00032035483683129785</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>0.003807257584770962 +/- 0.0005452201897627493</t>
+          <t>0.0003866745984533071 +/- 0.0007986746925697417</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>0.0021415823914336827 +/- 0.0016815340898396858</t>
+          <t>0.009875074360499702 +/- 0.0017786932049644255</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-0.006781677572873279 +/- 0.0008069399147085445</t>
+          <t>-0.002795954788816157 +/- 0.0011986580416186816</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-0.011362284354550844 +/- 0.001768717281061094</t>
+          <t>-0.008120166567519327 +/- 0.0013568702829216826</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-0.003093396787626401 +/- 0.0007188010692203798</t>
+          <t>-0.0013384889946460254 +/- 0.0007436049970255865</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>-0.0020523497917905864 +/- 0.000505651397977392</t>
+          <t>-0.0005056513979773802 +/- 0.0005160425809904054</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0.0013087447947650378 +/- 0.00033121739219688404</t>
+          <t>-0.0003569303985722527 +/- 0.00032035483683129785</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>-0.00032718619869124275 +/- 0.0012927610834087351</t>
+          <t>0.004402141582391439 +/- 0.001443743140929418</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.008685306365258794 +/- 0.001803391599193834</t>
+          <t>0.004550862581796544 +/- 0.0013954436770660318</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>-0.000446162998215327 +/- 0.0007070115600240739</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>0.006900654372397397 +/- 0.0014064949931632059</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>0.0031231409875074447 +/- 0.0015297312160171197</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>-0.001130279595478878 +/- 0.0004941477610302318</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>0.0031826293872694645 +/- 0.0012049154729642558</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>0.0006543723973825077 +/- 0.001449858132891599</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>0.006484235574063057 +/- 0.0019988456414528873</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>0.002974419988102317 +/- 0.0011208473338142088</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0.0006543723973824855 +/- 0.00022258521039704467</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>0.0031826293872694866 +/- 0.0010562332483381707</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>0.0006543723973825189 +/- 0.0006756583397739964</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>0.0009815585960737505 +/- 0.0005329111501240092</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>0.008179654967281402 +/- 0.001924199165929322</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>-0.004402141582391406 +/- 0.0013288701905823145</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>0.0005948839976204657 +/- 0.0014077524766447577</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>0.0005948839976204545 +/- 0.00026604021148125427</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>0.0013087447947650265 +/- 0.0006267491822041863</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>0.0007138607971445609 +/- 0.000979302655154904</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>0.0018738845925044712 +/- 0.0007045044189367752</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>0.004699583581201672 +/- 0.0011808110197072583</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
           <t>2.9744199881021062e-05 +/- 8.923259964306317e-05</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>-8.923259964305208e-05 +/- 0.0006246281975014914</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>-0.0016359309934562472 +/- 0.0011228189225566212</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>-0.011094586555621644 +/- 0.001703748184606753</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>-0.0022010707911956917 +/- 0.0006937479946276465</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>-0.001189767995240909 +/- 0.0008620688129797437</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>-0.003361094586555602 +/- 0.0013633749716080678</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>-0.002676977989292062 +/- 0.002034816344614779</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>0.0007733491969066364 +/- 0.0011838042083362622</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>-0.00020820939916713633 +/- 0.00040016728278029424</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>-0.0025877453896489986 +/- 0.0014755641588117196</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>-0.00047590719809634805 +/- 0.0009041453987847156</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>-0.0006246281975014866 +/- 0.0008140352280430829</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>0.0023497917906008413 +/- 0.0009541353320847963</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>-0.006186793575252825 +/- 0.0010790218410004094</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>0.005234979179060084 +/- 0.001546698393813216</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>-0.0003271861986912317 +/- 0.0002470738805150945</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>-0.0005353955978583902 +/- 0.0007847058868693151</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>0.0005948839976204878 +/- 0.000678272114871587</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>0.0011302795954789002 +/- 0.0007138607971445554</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>-0.0011302795954788558 +/- 0.0014978796326013185</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.00018811883760667172</t>
-        </is>
-      </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>0.0004759071980963814 +/- 0.0005674831656257948</t>
+          <t>-8.923259964305208e-05 +/- 0.0006523412313938269</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>-0.0024985127900059136 +/- 0.0008538191608808483</t>
+          <t>0.00184414039262345 +/- 0.0016442920834128807</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>-0.00258774538964901 +/- 0.0016020503283159355</t>
+          <t>0.0030933967876264233 +/- 0.0014400616819643275</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>-0.0002676977989291895 +/- 0.0007807498363121202</t>
+          <t>0.0009815585960737615 +/- 0.0005329111501240074</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>-0.004372397382510396 +/- 0.0013437664483136838</t>
+          <t>-0.0013979773944080675 +/- 0.001105348255565858</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>-0.003004164187983327 +/- 0.0013463974179364934</t>
+          <t>-0.0026769779892920733 +/- 0.0013302010574061818</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>0.0016954193932183336 +/- 0.0006918324419757704</t>
+          <t>-0.00047590719809635916 +/- 0.0014764632535384594</t>
         </is>
       </c>
     </row>
